--- a/research/traditional_assets/database/data/qatar/qatar_computer_services.xlsx
+++ b/research/traditional_assets/database/data/qatar/qatar_computer_services.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09530633522039031</v>
+        <v>0.09525152888516991</v>
       </c>
       <c r="C2">
-        <v>660.1722039742828</v>
+        <v>654.2326046565295</v>
       </c>
       <c r="D2">
-        <v>594.0722039742827</v>
+        <v>594.7306046565294</v>
       </c>
       <c r="E2">
-        <v>-76</v>
+        <v>-69.402</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>6.598</v>
       </c>
       <c r="G2">
         <v>66.09999999999999</v>
@@ -1439,28 +1439,28 @@
         <v>35.635</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.3318794</v>
       </c>
       <c r="N2">
-        <v>35.635</v>
+        <v>35.3031206</v>
       </c>
       <c r="O2">
-        <v>3.5635</v>
+        <v>3.53031206</v>
       </c>
       <c r="P2">
-        <v>32.0715</v>
+        <v>31.77280854</v>
       </c>
       <c r="Q2">
-        <v>33.5615</v>
+        <v>33.26280854</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09530633522039031</v>
+        <v>0.09575639281330295</v>
       </c>
       <c r="T2">
-        <v>0.9922881498763957</v>
+        <v>1.001308951238908</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>107.3733410389437</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09525152888516991</v>
+        <v>0.09519672254994953</v>
       </c>
       <c r="C3">
-        <v>654.2326046565295</v>
+        <v>648.2944663477917</v>
       </c>
       <c r="D3">
-        <v>594.7306046565294</v>
+        <v>595.3904663477917</v>
       </c>
       <c r="E3">
-        <v>-69.402</v>
+        <v>-62.804</v>
       </c>
       <c r="F3">
-        <v>6.598</v>
+        <v>13.196</v>
       </c>
       <c r="G3">
         <v>66.09999999999999</v>
@@ -1521,28 +1521,28 @@
         <v>35.635</v>
       </c>
       <c r="M3">
-        <v>0.3318794</v>
+        <v>0.6637588</v>
       </c>
       <c r="N3">
-        <v>35.3031206</v>
+        <v>34.9712412</v>
       </c>
       <c r="O3">
-        <v>3.53031206</v>
+        <v>3.497124120000001</v>
       </c>
       <c r="P3">
-        <v>31.77280854</v>
+        <v>31.47411708</v>
       </c>
       <c r="Q3">
-        <v>33.26280854</v>
+        <v>32.96411708</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09575639281330295</v>
+        <v>0.09621563525505054</v>
       </c>
       <c r="T3">
-        <v>1.001308951238908</v>
+        <v>1.010513850588411</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>107.3733410389437</v>
+        <v>53.68667051947184</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09519672254994953</v>
+        <v>0.09514191621472914</v>
       </c>
       <c r="C4">
-        <v>648.2944663477917</v>
+        <v>642.3577939164998</v>
       </c>
       <c r="D4">
-        <v>595.3904663477917</v>
+        <v>596.0517939164997</v>
       </c>
       <c r="E4">
-        <v>-62.804</v>
+        <v>-56.206</v>
       </c>
       <c r="F4">
-        <v>13.196</v>
+        <v>19.794</v>
       </c>
       <c r="G4">
         <v>66.09999999999999</v>
@@ -1603,28 +1603,28 @@
         <v>35.635</v>
       </c>
       <c r="M4">
-        <v>0.6637588</v>
+        <v>0.9956381999999998</v>
       </c>
       <c r="N4">
-        <v>34.9712412</v>
+        <v>34.6393618</v>
       </c>
       <c r="O4">
-        <v>3.497124120000001</v>
+        <v>3.46393618</v>
       </c>
       <c r="P4">
-        <v>31.47411708</v>
+        <v>31.17542562</v>
       </c>
       <c r="Q4">
-        <v>32.96411708</v>
+        <v>32.66542561999999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09621563525505054</v>
+        <v>0.09668434661312283</v>
       </c>
       <c r="T4">
-        <v>1.010513850588411</v>
+        <v>1.019908541677079</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>53.68667051947184</v>
+        <v>35.79111367964789</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09514191621472914</v>
+        <v>0.09508710987950876</v>
       </c>
       <c r="C5">
-        <v>642.3577939164998</v>
+        <v>636.4225922527372</v>
       </c>
       <c r="D5">
-        <v>596.0517939164997</v>
+        <v>596.7145922527372</v>
       </c>
       <c r="E5">
-        <v>-56.206</v>
+        <v>-49.608</v>
       </c>
       <c r="F5">
-        <v>19.794</v>
+        <v>26.392</v>
       </c>
       <c r="G5">
         <v>66.09999999999999</v>
@@ -1685,28 +1685,28 @@
         <v>35.635</v>
       </c>
       <c r="M5">
-        <v>0.9956381999999998</v>
+        <v>1.3275176</v>
       </c>
       <c r="N5">
-        <v>34.6393618</v>
+        <v>34.3074824</v>
       </c>
       <c r="O5">
-        <v>3.46393618</v>
+        <v>3.43074824</v>
       </c>
       <c r="P5">
-        <v>31.17542562</v>
+        <v>30.87673416</v>
       </c>
       <c r="Q5">
-        <v>32.66542561999999</v>
+        <v>32.36673416</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09668434661312283</v>
+        <v>0.09716282279115496</v>
       </c>
       <c r="T5">
-        <v>1.019908541677079</v>
+        <v>1.029498955496761</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>35.79111367964789</v>
+        <v>26.84333525973592</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09508710987950876</v>
+        <v>0.09503230354428835</v>
       </c>
       <c r="C6">
-        <v>636.4225922527372</v>
+        <v>630.4888662683639</v>
       </c>
       <c r="D6">
-        <v>596.7145922527372</v>
+        <v>597.3788662683639</v>
       </c>
       <c r="E6">
-        <v>-49.608</v>
+        <v>-43.01</v>
       </c>
       <c r="F6">
-        <v>26.392</v>
+        <v>32.99</v>
       </c>
       <c r="G6">
         <v>66.09999999999999</v>
@@ -1767,28 +1767,28 @@
         <v>35.635</v>
       </c>
       <c r="M6">
-        <v>1.3275176</v>
+        <v>1.659397</v>
       </c>
       <c r="N6">
-        <v>34.3074824</v>
+        <v>33.975603</v>
       </c>
       <c r="O6">
-        <v>3.43074824</v>
+        <v>3.3975603</v>
       </c>
       <c r="P6">
-        <v>30.87673416</v>
+        <v>30.5780427</v>
       </c>
       <c r="Q6">
-        <v>32.36673416</v>
+        <v>32.0680427</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09716282279115496</v>
+        <v>0.09765137215188248</v>
       </c>
       <c r="T6">
-        <v>1.029498955496761</v>
+        <v>1.039291272765277</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>26.84333525973592</v>
+        <v>21.47466820778873</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09503230354428835</v>
+        <v>0.09497749720906797</v>
       </c>
       <c r="C7">
-        <v>630.4888662683639</v>
+        <v>624.5566208971344</v>
       </c>
       <c r="D7">
-        <v>597.3788662683639</v>
+        <v>598.0446208971343</v>
       </c>
       <c r="E7">
-        <v>-43.01</v>
+        <v>-36.412</v>
       </c>
       <c r="F7">
-        <v>32.99</v>
+        <v>39.588</v>
       </c>
       <c r="G7">
         <v>66.09999999999999</v>
@@ -1849,28 +1849,28 @@
         <v>35.635</v>
       </c>
       <c r="M7">
-        <v>1.659397</v>
+        <v>1.9912764</v>
       </c>
       <c r="N7">
-        <v>33.975603</v>
+        <v>33.6437236</v>
       </c>
       <c r="O7">
-        <v>3.3975603</v>
+        <v>3.36437236</v>
       </c>
       <c r="P7">
-        <v>30.5780427</v>
+        <v>30.27935124</v>
       </c>
       <c r="Q7">
-        <v>32.0680427</v>
+        <v>31.76935124</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09765137215188248</v>
+        <v>0.09815031617985955</v>
       </c>
       <c r="T7">
-        <v>1.039291272765277</v>
+        <v>1.04929193720972</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>21.47466820778873</v>
+        <v>17.89555683982394</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09497749720906797</v>
+        <v>0.0949226908738476</v>
       </c>
       <c r="C8">
-        <v>624.5566208971344</v>
+        <v>618.6258610948223</v>
       </c>
       <c r="D8">
-        <v>598.0446208971343</v>
+        <v>598.7118610948223</v>
       </c>
       <c r="E8">
-        <v>-36.41200000000001</v>
+        <v>-29.81400000000001</v>
       </c>
       <c r="F8">
-        <v>39.58799999999999</v>
+        <v>46.18599999999999</v>
       </c>
       <c r="G8">
         <v>66.09999999999999</v>
@@ -1931,28 +1931,28 @@
         <v>35.635</v>
       </c>
       <c r="M8">
-        <v>1.9912764</v>
+        <v>2.323155799999999</v>
       </c>
       <c r="N8">
-        <v>33.6437236</v>
+        <v>33.3118442</v>
       </c>
       <c r="O8">
-        <v>3.36437236</v>
+        <v>3.33118442</v>
       </c>
       <c r="P8">
-        <v>30.27935124</v>
+        <v>29.98065978</v>
       </c>
       <c r="Q8">
-        <v>31.76935124</v>
+        <v>31.47065977999999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09815031617985955</v>
+        <v>0.09865999018693289</v>
       </c>
       <c r="T8">
-        <v>1.04929193720972</v>
+        <v>1.059507669706732</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>17.89555683982395</v>
+        <v>15.3390487198491</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09492269087384758</v>
+        <v>0.0948678845386272</v>
       </c>
       <c r="C9">
-        <v>618.6258610948224</v>
+        <v>612.6965918393433</v>
       </c>
       <c r="D9">
-        <v>598.7118610948224</v>
+        <v>599.3805918393433</v>
       </c>
       <c r="E9">
-        <v>-29.814</v>
+        <v>-23.216</v>
       </c>
       <c r="F9">
-        <v>46.186</v>
+        <v>52.784</v>
       </c>
       <c r="G9">
         <v>66.09999999999999</v>
@@ -2013,28 +2013,28 @@
         <v>35.635</v>
       </c>
       <c r="M9">
-        <v>2.3231558</v>
+        <v>2.6550352</v>
       </c>
       <c r="N9">
-        <v>33.3118442</v>
+        <v>32.9799648</v>
       </c>
       <c r="O9">
-        <v>3.33118442</v>
+        <v>3.29799648</v>
       </c>
       <c r="P9">
-        <v>29.98065978</v>
+        <v>29.68196832</v>
       </c>
       <c r="Q9">
-        <v>31.47065977999999</v>
+        <v>31.17196831999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09865999018693289</v>
+        <v>0.09918074406372521</v>
       </c>
       <c r="T9">
-        <v>1.059507669706732</v>
+        <v>1.069945483344983</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>15.33904871984909</v>
+        <v>13.42166762986796</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0948678845386272</v>
+        <v>0.0949345782034068</v>
       </c>
       <c r="C10">
-        <v>612.6965918393433</v>
+        <v>605.2850122843904</v>
       </c>
       <c r="D10">
-        <v>599.3805918393433</v>
+        <v>598.5670122843903</v>
       </c>
       <c r="E10">
-        <v>-23.216</v>
+        <v>-16.61800000000001</v>
       </c>
       <c r="F10">
-        <v>52.784</v>
+        <v>59.38199999999999</v>
       </c>
       <c r="G10">
         <v>66.09999999999999</v>
@@ -2095,45 +2095,45 @@
         <v>35.635</v>
       </c>
       <c r="M10">
-        <v>2.6550352</v>
+        <v>3.075987599999999</v>
       </c>
       <c r="N10">
-        <v>32.9799648</v>
+        <v>32.5590124</v>
       </c>
       <c r="O10">
-        <v>3.29799648</v>
+        <v>3.25590124</v>
       </c>
       <c r="P10">
-        <v>29.68196832</v>
+        <v>29.30311116</v>
       </c>
       <c r="Q10">
-        <v>31.17196831999999</v>
+        <v>30.79311116</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09918074406372521</v>
+        <v>0.0997129430806668</v>
       </c>
       <c r="T10">
-        <v>1.069945483344983</v>
+        <v>1.080612699480778</v>
       </c>
       <c r="U10">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V10">
         <v>0.1</v>
       </c>
       <c r="W10">
-        <v>0.04527</v>
+        <v>0.04662</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>13.42166762986796</v>
+        <v>11.58489715628243</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0949345782034068</v>
+        <v>0.09489327186818641</v>
       </c>
       <c r="C11">
-        <v>605.2850122843904</v>
+        <v>599.1906375006454</v>
       </c>
       <c r="D11">
-        <v>598.5670122843903</v>
+        <v>599.0706375006454</v>
       </c>
       <c r="E11">
-        <v>-16.61800000000001</v>
+        <v>-10.02000000000001</v>
       </c>
       <c r="F11">
-        <v>59.38199999999999</v>
+        <v>65.97999999999999</v>
       </c>
       <c r="G11">
         <v>66.09999999999999</v>
@@ -2177,28 +2177,28 @@
         <v>35.635</v>
       </c>
       <c r="M11">
-        <v>3.075987599999999</v>
+        <v>3.417764</v>
       </c>
       <c r="N11">
-        <v>32.5590124</v>
+        <v>32.217236</v>
       </c>
       <c r="O11">
-        <v>3.25590124</v>
+        <v>3.2217236</v>
       </c>
       <c r="P11">
-        <v>29.30311116</v>
+        <v>28.9955124</v>
       </c>
       <c r="Q11">
-        <v>30.79311116</v>
+        <v>30.4855124</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.0997129430806668</v>
+        <v>0.1002569687424293</v>
       </c>
       <c r="T11">
-        <v>1.080612699480778</v>
+        <v>1.091516964864035</v>
       </c>
       <c r="U11">
         <v>0.0518</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>11.58489715628243</v>
+        <v>10.42640744065418</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09489327186818641</v>
+        <v>0.09502026553296601</v>
       </c>
       <c r="C12">
-        <v>599.1906375006454</v>
+        <v>591.0469697783308</v>
       </c>
       <c r="D12">
-        <v>599.0706375006454</v>
+        <v>597.5249697783307</v>
       </c>
       <c r="E12">
-        <v>-10.02</v>
+        <v>-3.422000000000011</v>
       </c>
       <c r="F12">
-        <v>65.98</v>
+        <v>72.57799999999999</v>
       </c>
       <c r="G12">
         <v>66.09999999999999</v>
@@ -2259,45 +2259,45 @@
         <v>35.635</v>
       </c>
       <c r="M12">
-        <v>3.417764</v>
+        <v>3.882922999999999</v>
       </c>
       <c r="N12">
-        <v>32.217236</v>
+        <v>31.752077</v>
       </c>
       <c r="O12">
-        <v>3.2217236</v>
+        <v>3.1752077</v>
       </c>
       <c r="P12">
-        <v>28.9955124</v>
+        <v>28.5768693</v>
       </c>
       <c r="Q12">
-        <v>30.4855124</v>
+        <v>30.0668693</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1002569687424293</v>
+        <v>0.1008132196999618</v>
       </c>
       <c r="T12">
-        <v>1.091516964864035</v>
+        <v>1.102666269918826</v>
       </c>
       <c r="U12">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V12">
         <v>0.1</v>
       </c>
       <c r="W12">
-        <v>0.04662</v>
+        <v>0.04815</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>10.42640744065418</v>
+        <v>9.177364578179892</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09502026553296601</v>
+        <v>0.09499425919774565</v>
       </c>
       <c r="C13">
-        <v>591.0469697783308</v>
+        <v>584.7648488040547</v>
       </c>
       <c r="D13">
-        <v>597.5249697783307</v>
+        <v>597.8408488040546</v>
       </c>
       <c r="E13">
-        <v>-3.422000000000011</v>
+        <v>3.175999999999988</v>
       </c>
       <c r="F13">
-        <v>72.57799999999999</v>
+        <v>79.17599999999999</v>
       </c>
       <c r="G13">
         <v>66.09999999999999</v>
@@ -2341,28 +2341,28 @@
         <v>35.635</v>
       </c>
       <c r="M13">
-        <v>3.882922999999999</v>
+        <v>4.235916</v>
       </c>
       <c r="N13">
-        <v>31.752077</v>
+        <v>31.399084</v>
       </c>
       <c r="O13">
-        <v>3.1752077</v>
+        <v>3.1399084</v>
       </c>
       <c r="P13">
-        <v>28.5768693</v>
+        <v>28.2591756</v>
       </c>
       <c r="Q13">
-        <v>30.0668693</v>
+        <v>29.7491756</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1008132196999618</v>
+        <v>0.101382112724711</v>
       </c>
       <c r="T13">
-        <v>1.102666269918826</v>
+        <v>1.114068968270317</v>
       </c>
       <c r="U13">
         <v>0.0535</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>9.177364578179892</v>
+        <v>8.412584196664902</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09499425919774565</v>
+        <v>0.09496825286252523</v>
       </c>
       <c r="C14">
-        <v>584.7648488040547</v>
+        <v>578.4830619826259</v>
       </c>
       <c r="D14">
-        <v>597.8408488040546</v>
+        <v>598.1570619826259</v>
       </c>
       <c r="E14">
-        <v>3.175999999999988</v>
+        <v>9.774000000000001</v>
       </c>
       <c r="F14">
-        <v>79.17599999999999</v>
+        <v>85.774</v>
       </c>
       <c r="G14">
         <v>66.09999999999999</v>
@@ -2423,28 +2423,28 @@
         <v>35.635</v>
       </c>
       <c r="M14">
-        <v>4.235916</v>
+        <v>4.588909</v>
       </c>
       <c r="N14">
-        <v>31.399084</v>
+        <v>31.046091</v>
       </c>
       <c r="O14">
-        <v>3.1399084</v>
+        <v>3.1046091</v>
       </c>
       <c r="P14">
-        <v>28.2591756</v>
+        <v>27.9414819</v>
       </c>
       <c r="Q14">
-        <v>29.7491756</v>
+        <v>29.43148189999999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.101382112724711</v>
+        <v>0.101964083750029</v>
       </c>
       <c r="T14">
-        <v>1.114068968270317</v>
+        <v>1.125733797618394</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>8.412584196664902</v>
+        <v>7.765462335382985</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09496825286252523</v>
+        <v>0.09504304652730484</v>
       </c>
       <c r="C15">
-        <v>578.4830619826259</v>
+        <v>570.9765406393196</v>
       </c>
       <c r="D15">
-        <v>598.1570619826259</v>
+        <v>597.2485406393196</v>
       </c>
       <c r="E15">
-        <v>9.774000000000001</v>
+        <v>16.372</v>
       </c>
       <c r="F15">
-        <v>85.774</v>
+        <v>92.372</v>
       </c>
       <c r="G15">
         <v>66.09999999999999</v>
@@ -2505,45 +2505,45 @@
         <v>35.635</v>
       </c>
       <c r="M15">
-        <v>4.588909</v>
+        <v>5.0157996</v>
       </c>
       <c r="N15">
-        <v>31.046091</v>
+        <v>30.6192004</v>
       </c>
       <c r="O15">
-        <v>3.1046091</v>
+        <v>3.06192004</v>
       </c>
       <c r="P15">
-        <v>27.9414819</v>
+        <v>27.55728036</v>
       </c>
       <c r="Q15">
-        <v>29.43148189999999</v>
+        <v>29.04728035999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.101964083750029</v>
+        <v>0.1025595889852382</v>
       </c>
       <c r="T15">
-        <v>1.125733797618394</v>
+        <v>1.137669902067588</v>
       </c>
       <c r="U15">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V15">
         <v>0.1</v>
       </c>
       <c r="W15">
-        <v>0.04815</v>
+        <v>0.04887</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y15">
-        <v>7.765462335382985</v>
+        <v>7.104550189764359</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09504304652730484</v>
+        <v>0.09502424019208446</v>
       </c>
       <c r="C16">
-        <v>570.9765406393196</v>
+        <v>564.606722043874</v>
       </c>
       <c r="D16">
-        <v>597.2485406393196</v>
+        <v>597.476722043874</v>
       </c>
       <c r="E16">
-        <v>16.372</v>
+        <v>22.97000000000001</v>
       </c>
       <c r="F16">
-        <v>92.372</v>
+        <v>98.97000000000001</v>
       </c>
       <c r="G16">
         <v>66.09999999999999</v>
@@ -2587,28 +2587,28 @@
         <v>35.635</v>
       </c>
       <c r="M16">
-        <v>5.0157996</v>
+        <v>5.374071000000001</v>
       </c>
       <c r="N16">
-        <v>30.6192004</v>
+        <v>30.260929</v>
       </c>
       <c r="O16">
-        <v>3.06192004</v>
+        <v>3.0260929</v>
       </c>
       <c r="P16">
-        <v>27.55728036</v>
+        <v>27.2348361</v>
       </c>
       <c r="Q16">
-        <v>29.04728035999999</v>
+        <v>28.72483609999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1025595889852382</v>
+        <v>0.1031691061083347</v>
       </c>
       <c r="T16">
-        <v>1.137669902067588</v>
+        <v>1.149886856033235</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>7.104550189764359</v>
+        <v>6.630913510446734</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09502424019208446</v>
+        <v>0.09500543385686407</v>
       </c>
       <c r="C17">
-        <v>564.606722043874</v>
+        <v>558.2370778704646</v>
       </c>
       <c r="D17">
-        <v>597.476722043874</v>
+        <v>597.7050778704646</v>
       </c>
       <c r="E17">
-        <v>22.96999999999998</v>
+        <v>29.568</v>
       </c>
       <c r="F17">
-        <v>98.96999999999998</v>
+        <v>105.568</v>
       </c>
       <c r="G17">
         <v>66.09999999999999</v>
@@ -2669,28 +2669,28 @@
         <v>35.635</v>
       </c>
       <c r="M17">
-        <v>5.374070999999999</v>
+        <v>5.7323424</v>
       </c>
       <c r="N17">
-        <v>30.260929</v>
+        <v>29.9026576</v>
       </c>
       <c r="O17">
-        <v>3.0260929</v>
+        <v>2.99026576</v>
       </c>
       <c r="P17">
-        <v>27.2348361</v>
+        <v>26.91239184</v>
       </c>
       <c r="Q17">
-        <v>28.72483609999999</v>
+        <v>28.40239184</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1031691061083347</v>
+        <v>0.1037931355438858</v>
       </c>
       <c r="T17">
-        <v>1.149886856033235</v>
+        <v>1.162394689855206</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>6.630913510446736</v>
+        <v>6.216481416043814</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09500543385686407</v>
+        <v>0.09513962752164368</v>
       </c>
       <c r="C18">
-        <v>558.2370778704646</v>
+        <v>550.013442678516</v>
       </c>
       <c r="D18">
-        <v>597.7050778704646</v>
+        <v>596.079442678516</v>
       </c>
       <c r="E18">
-        <v>29.568</v>
+        <v>36.166</v>
       </c>
       <c r="F18">
-        <v>105.568</v>
+        <v>112.166</v>
       </c>
       <c r="G18">
         <v>66.09999999999999</v>
@@ -2751,45 +2751,45 @@
         <v>35.635</v>
       </c>
       <c r="M18">
-        <v>5.7323424</v>
+        <v>6.2027798</v>
       </c>
       <c r="N18">
-        <v>29.9026576</v>
+        <v>29.4322202</v>
       </c>
       <c r="O18">
-        <v>2.99026576</v>
+        <v>2.94322202</v>
       </c>
       <c r="P18">
-        <v>26.91239184</v>
+        <v>26.48899818</v>
       </c>
       <c r="Q18">
-        <v>28.40239184</v>
+        <v>27.97899817999999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1037931355438858</v>
+        <v>0.1044322018333056</v>
       </c>
       <c r="T18">
-        <v>1.162394689855206</v>
+        <v>1.175203917263249</v>
       </c>
       <c r="U18">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V18">
         <v>0.1</v>
       </c>
       <c r="W18">
-        <v>0.04887</v>
+        <v>0.04977</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y18">
-        <v>6.216481416043814</v>
+        <v>5.745004844440874</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09513962752164368</v>
+        <v>0.09512982118642328</v>
       </c>
       <c r="C19">
-        <v>550.013442678516</v>
+        <v>543.5339380367457</v>
       </c>
       <c r="D19">
-        <v>596.079442678516</v>
+        <v>596.1979380367457</v>
       </c>
       <c r="E19">
-        <v>36.166</v>
+        <v>42.76400000000001</v>
       </c>
       <c r="F19">
-        <v>112.166</v>
+        <v>118.764</v>
       </c>
       <c r="G19">
         <v>66.09999999999999</v>
@@ -2833,28 +2833,28 @@
         <v>35.635</v>
       </c>
       <c r="M19">
-        <v>6.2027798</v>
+        <v>6.567649200000001</v>
       </c>
       <c r="N19">
-        <v>29.4322202</v>
+        <v>29.0673508</v>
       </c>
       <c r="O19">
-        <v>2.94322202</v>
+        <v>2.90673508</v>
       </c>
       <c r="P19">
-        <v>26.48899818</v>
+        <v>26.16061572</v>
       </c>
       <c r="Q19">
-        <v>27.97899817999999</v>
+        <v>27.65061571999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1044322018333056</v>
+        <v>0.1050868551053943</v>
       </c>
       <c r="T19">
-        <v>1.175203917263249</v>
+        <v>1.188325564851976</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.745004844440874</v>
+        <v>5.425837908638603</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0951298211864233</v>
+        <v>0.0951200148512029</v>
       </c>
       <c r="C20">
-        <v>543.5339380367456</v>
+        <v>537.0544805160156</v>
       </c>
       <c r="D20">
-        <v>596.1979380367455</v>
+        <v>596.3164805160155</v>
       </c>
       <c r="E20">
-        <v>42.76399999999998</v>
+        <v>49.36199999999999</v>
       </c>
       <c r="F20">
-        <v>118.764</v>
+        <v>125.362</v>
       </c>
       <c r="G20">
         <v>66.09999999999999</v>
@@ -2915,28 +2915,28 @@
         <v>35.635</v>
       </c>
       <c r="M20">
-        <v>6.567649199999999</v>
+        <v>6.9325186</v>
       </c>
       <c r="N20">
-        <v>29.0673508</v>
+        <v>28.7024814</v>
       </c>
       <c r="O20">
-        <v>2.90673508</v>
+        <v>2.87024814</v>
       </c>
       <c r="P20">
-        <v>26.16061572</v>
+        <v>25.83223326</v>
       </c>
       <c r="Q20">
-        <v>27.65061572</v>
+        <v>27.32223325999999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1050868551053943</v>
+        <v>0.105757672655806</v>
       </c>
       <c r="T20">
-        <v>1.188325564851976</v>
+        <v>1.20177120373919</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.425837908638605</v>
+        <v>5.140267492394466</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0951200148512029</v>
+        <v>0.09511020851598252</v>
       </c>
       <c r="C21">
-        <v>537.0544805160156</v>
+        <v>530.5750701444387</v>
       </c>
       <c r="D21">
-        <v>596.3164805160155</v>
+        <v>596.4350701444387</v>
       </c>
       <c r="E21">
-        <v>49.36199999999999</v>
+        <v>55.96000000000001</v>
       </c>
       <c r="F21">
-        <v>125.362</v>
+        <v>131.96</v>
       </c>
       <c r="G21">
         <v>66.09999999999999</v>
@@ -2997,28 +2997,28 @@
         <v>35.635</v>
       </c>
       <c r="M21">
-        <v>6.9325186</v>
+        <v>7.297388000000001</v>
       </c>
       <c r="N21">
-        <v>28.7024814</v>
+        <v>28.337612</v>
       </c>
       <c r="O21">
-        <v>2.87024814</v>
+        <v>2.8337612</v>
       </c>
       <c r="P21">
-        <v>25.83223326</v>
+        <v>25.5038508</v>
       </c>
       <c r="Q21">
-        <v>27.32223325999999</v>
+        <v>26.99385079999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.105757672655806</v>
+        <v>0.1064452606449781</v>
       </c>
       <c r="T21">
-        <v>1.20177120373919</v>
+        <v>1.215552983598585</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.140267492394466</v>
+        <v>4.883254117774743</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09511020851598252</v>
+        <v>0.09510040218076213</v>
       </c>
       <c r="C22">
-        <v>530.5750701444387</v>
+        <v>524.0957069501507</v>
       </c>
       <c r="D22">
-        <v>596.4350701444387</v>
+        <v>596.5537069501506</v>
       </c>
       <c r="E22">
-        <v>55.96000000000001</v>
+        <v>62.55799999999999</v>
       </c>
       <c r="F22">
-        <v>131.96</v>
+        <v>138.558</v>
       </c>
       <c r="G22">
         <v>66.09999999999999</v>
@@ -3079,28 +3079,28 @@
         <v>35.635</v>
       </c>
       <c r="M22">
-        <v>7.297388000000001</v>
+        <v>7.6622574</v>
       </c>
       <c r="N22">
-        <v>28.337612</v>
+        <v>27.9727426</v>
       </c>
       <c r="O22">
-        <v>2.8337612</v>
+        <v>2.79727426</v>
       </c>
       <c r="P22">
-        <v>25.5038508</v>
+        <v>25.17546833999999</v>
       </c>
       <c r="Q22">
-        <v>26.99385079999999</v>
+        <v>26.66546833999999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1064452606449781</v>
+        <v>0.1071502559250153</v>
       </c>
       <c r="T22">
-        <v>1.215552983598585</v>
+        <v>1.229683669277204</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>4.883254117774743</v>
+        <v>4.650718207404518</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09510040218076211</v>
+        <v>0.09558559584554174</v>
       </c>
       <c r="C23">
-        <v>524.0957069501508</v>
+        <v>511.6838952562824</v>
       </c>
       <c r="D23">
-        <v>596.5537069501507</v>
+        <v>590.7398952562824</v>
       </c>
       <c r="E23">
-        <v>62.55799999999999</v>
+        <v>69.15599999999998</v>
       </c>
       <c r="F23">
-        <v>138.558</v>
+        <v>145.156</v>
       </c>
       <c r="G23">
         <v>66.09999999999999</v>
@@ -3161,45 +3161,45 @@
         <v>35.635</v>
       </c>
       <c r="M23">
-        <v>7.6622574</v>
+        <v>8.3900168</v>
       </c>
       <c r="N23">
-        <v>27.9727426</v>
+        <v>27.2449832</v>
       </c>
       <c r="O23">
-        <v>2.79727426</v>
+        <v>2.72449832</v>
       </c>
       <c r="P23">
-        <v>25.17546833999999</v>
+        <v>24.52048488</v>
       </c>
       <c r="Q23">
-        <v>26.66546833999999</v>
+        <v>26.01048488</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1071502559250153</v>
+        <v>0.1078733280071048</v>
       </c>
       <c r="T23">
-        <v>1.229683669277204</v>
+        <v>1.244176680229635</v>
       </c>
       <c r="U23">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V23">
         <v>0.1</v>
       </c>
       <c r="W23">
-        <v>0.04977</v>
+        <v>0.05202</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y23">
-        <v>4.650718207404518</v>
+        <v>4.247309731251075</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09558559584554174</v>
+        <v>0.09559828951032134</v>
       </c>
       <c r="C24">
-        <v>511.6838952562824</v>
+        <v>504.9353146986757</v>
       </c>
       <c r="D24">
-        <v>590.7398952562824</v>
+        <v>590.5893146986757</v>
       </c>
       <c r="E24">
-        <v>69.15599999999998</v>
+        <v>75.75399999999999</v>
       </c>
       <c r="F24">
-        <v>145.156</v>
+        <v>151.754</v>
       </c>
       <c r="G24">
         <v>66.09999999999999</v>
@@ -3243,28 +3243,28 @@
         <v>35.635</v>
       </c>
       <c r="M24">
-        <v>8.3900168</v>
+        <v>8.7713812</v>
       </c>
       <c r="N24">
-        <v>27.2449832</v>
+        <v>26.8636188</v>
       </c>
       <c r="O24">
-        <v>2.72449832</v>
+        <v>2.68636188</v>
       </c>
       <c r="P24">
-        <v>24.52048488</v>
+        <v>24.17725692</v>
       </c>
       <c r="Q24">
-        <v>26.01048488</v>
+        <v>25.66725692</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1078733280071048</v>
+        <v>0.1086151811822355</v>
       </c>
       <c r="T24">
-        <v>1.244176680229635</v>
+        <v>1.259046133024985</v>
       </c>
       <c r="U24">
         <v>0.0578</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.247309731251075</v>
+        <v>4.062644090761896</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09559828951032134</v>
+        <v>0.09636698317510095</v>
       </c>
       <c r="C25">
-        <v>504.9353146986757</v>
+        <v>489.3594750849624</v>
       </c>
       <c r="D25">
-        <v>590.5893146986757</v>
+        <v>581.6114750849623</v>
       </c>
       <c r="E25">
-        <v>75.75399999999999</v>
+        <v>82.352</v>
       </c>
       <c r="F25">
-        <v>151.754</v>
+        <v>158.352</v>
       </c>
       <c r="G25">
         <v>66.09999999999999</v>
@@ -3325,45 +3325,45 @@
         <v>35.635</v>
       </c>
       <c r="M25">
-        <v>8.7713812</v>
+        <v>9.7069776</v>
       </c>
       <c r="N25">
-        <v>26.8636188</v>
+        <v>25.9280224</v>
       </c>
       <c r="O25">
-        <v>2.68636188</v>
+        <v>2.59280224</v>
       </c>
       <c r="P25">
-        <v>24.17725692</v>
+        <v>23.33522016</v>
       </c>
       <c r="Q25">
-        <v>25.66725692</v>
+        <v>24.82522015999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1086151811822355</v>
+        <v>0.1093765568093434</v>
       </c>
       <c r="T25">
-        <v>1.259046133024985</v>
+        <v>1.274306887209687</v>
       </c>
       <c r="U25">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V25">
         <v>0.1</v>
       </c>
       <c r="W25">
-        <v>0.05202</v>
+        <v>0.05517</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>4.062644090761896</v>
+        <v>3.671070591529952</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09636698317510095</v>
+        <v>0.09641117683988056</v>
       </c>
       <c r="C26">
-        <v>489.3594750849624</v>
+        <v>482.253612115421</v>
       </c>
       <c r="D26">
-        <v>581.6114750849623</v>
+        <v>581.103612115421</v>
       </c>
       <c r="E26">
-        <v>82.35199999999998</v>
+        <v>88.94999999999999</v>
       </c>
       <c r="F26">
-        <v>158.352</v>
+        <v>164.95</v>
       </c>
       <c r="G26">
         <v>66.09999999999999</v>
@@ -3407,28 +3407,28 @@
         <v>35.635</v>
       </c>
       <c r="M26">
-        <v>9.706977599999998</v>
+        <v>10.111435</v>
       </c>
       <c r="N26">
-        <v>25.9280224</v>
+        <v>25.523565</v>
       </c>
       <c r="O26">
-        <v>2.59280224</v>
+        <v>2.5523565</v>
       </c>
       <c r="P26">
-        <v>23.33522016</v>
+        <v>22.9712085</v>
       </c>
       <c r="Q26">
-        <v>24.82522016</v>
+        <v>24.46120849999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1093765568093434</v>
+        <v>0.1101582357865074</v>
       </c>
       <c r="T26">
-        <v>1.274306887209687</v>
+        <v>1.289974594839314</v>
       </c>
       <c r="U26">
         <v>0.0613</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.671070591529953</v>
+        <v>3.524227767868754</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09641117683988056</v>
+        <v>0.09711057050466017</v>
       </c>
       <c r="C27">
-        <v>482.253612115421</v>
+        <v>467.7348234573187</v>
       </c>
       <c r="D27">
-        <v>581.103612115421</v>
+        <v>573.1828234573187</v>
       </c>
       <c r="E27">
-        <v>88.94999999999999</v>
+        <v>95.548</v>
       </c>
       <c r="F27">
-        <v>164.95</v>
+        <v>171.548</v>
       </c>
       <c r="G27">
         <v>66.09999999999999</v>
@@ -3489,45 +3489,45 @@
         <v>35.635</v>
       </c>
       <c r="M27">
-        <v>10.111435</v>
+        <v>10.9962268</v>
       </c>
       <c r="N27">
-        <v>25.523565</v>
+        <v>24.6387732</v>
       </c>
       <c r="O27">
-        <v>2.5523565</v>
+        <v>2.46387732</v>
       </c>
       <c r="P27">
-        <v>22.9712085</v>
+        <v>22.17489587999999</v>
       </c>
       <c r="Q27">
-        <v>24.46120849999999</v>
+        <v>23.66489587999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1101582357865074</v>
+        <v>0.1109610412225137</v>
       </c>
       <c r="T27">
-        <v>1.289974594839314</v>
+        <v>1.306065754026499</v>
       </c>
       <c r="U27">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V27">
         <v>0.1</v>
       </c>
       <c r="W27">
-        <v>0.05517</v>
+        <v>0.05769000000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y27">
-        <v>3.524227767868754</v>
+        <v>3.240657058837673</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09711057050466017</v>
+        <v>0.09717996416943979</v>
       </c>
       <c r="C28">
-        <v>467.7348234573187</v>
+        <v>460.3626840169474</v>
       </c>
       <c r="D28">
-        <v>573.1828234573187</v>
+        <v>572.4086840169473</v>
       </c>
       <c r="E28">
-        <v>95.548</v>
+        <v>102.146</v>
       </c>
       <c r="F28">
-        <v>171.548</v>
+        <v>178.146</v>
       </c>
       <c r="G28">
         <v>66.09999999999999</v>
@@ -3571,28 +3571,28 @@
         <v>35.635</v>
       </c>
       <c r="M28">
-        <v>10.9962268</v>
+        <v>11.4191586</v>
       </c>
       <c r="N28">
-        <v>24.6387732</v>
+        <v>24.2158414</v>
       </c>
       <c r="O28">
-        <v>2.46387732</v>
+        <v>2.42158414</v>
       </c>
       <c r="P28">
-        <v>22.17489587999999</v>
+        <v>21.79425726</v>
       </c>
       <c r="Q28">
-        <v>23.66489587999999</v>
+        <v>23.28425726</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1109610412225137</v>
+        <v>0.1117858413279997</v>
       </c>
       <c r="T28">
-        <v>1.306065754026499</v>
+        <v>1.322597766890045</v>
       </c>
       <c r="U28">
         <v>0.0641</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.240657058837673</v>
+        <v>3.120632723325167</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09717996416943979</v>
+        <v>0.0972493578342194</v>
       </c>
       <c r="C29">
-        <v>460.3626840169474</v>
+        <v>452.9926328581437</v>
       </c>
       <c r="D29">
-        <v>572.4086840169473</v>
+        <v>571.6366328581437</v>
       </c>
       <c r="E29">
-        <v>102.146</v>
+        <v>108.744</v>
       </c>
       <c r="F29">
-        <v>178.146</v>
+        <v>184.744</v>
       </c>
       <c r="G29">
         <v>66.09999999999999</v>
@@ -3653,28 +3653,28 @@
         <v>35.635</v>
       </c>
       <c r="M29">
-        <v>11.4191586</v>
+        <v>11.8420904</v>
       </c>
       <c r="N29">
-        <v>24.2158414</v>
+        <v>23.7929096</v>
       </c>
       <c r="O29">
-        <v>2.42158414</v>
+        <v>2.37929096</v>
       </c>
       <c r="P29">
-        <v>21.79425726</v>
+        <v>21.41361864</v>
       </c>
       <c r="Q29">
-        <v>23.28425726</v>
+        <v>22.90361864</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1117858413279997</v>
+        <v>0.1126335525475269</v>
       </c>
       <c r="T29">
-        <v>1.322597766890045</v>
+        <v>1.339589002333134</v>
       </c>
       <c r="U29">
         <v>0.0641</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.120632723325167</v>
+        <v>3.009181554634982</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0972493578342194</v>
+        <v>0.09935455149899901</v>
       </c>
       <c r="C30">
-        <v>452.9926328581437</v>
+        <v>423.9239784624776</v>
       </c>
       <c r="D30">
-        <v>571.6366328581437</v>
+        <v>549.1659784624776</v>
       </c>
       <c r="E30">
-        <v>108.744</v>
+        <v>115.342</v>
       </c>
       <c r="F30">
-        <v>184.744</v>
+        <v>191.342</v>
       </c>
       <c r="G30">
         <v>66.09999999999999</v>
@@ -3735,45 +3735,45 @@
         <v>35.635</v>
       </c>
       <c r="M30">
-        <v>11.8420904</v>
+        <v>13.7574898</v>
       </c>
       <c r="N30">
-        <v>23.7929096</v>
+        <v>21.8775102</v>
       </c>
       <c r="O30">
-        <v>2.37929096</v>
+        <v>2.18775102</v>
       </c>
       <c r="P30">
-        <v>21.41361864</v>
+        <v>19.68975918</v>
       </c>
       <c r="Q30">
-        <v>22.90361864</v>
+        <v>21.17975917999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1126335525475269</v>
+        <v>0.1135051429563366</v>
       </c>
       <c r="T30">
-        <v>1.339589002333134</v>
+        <v>1.357058864126733</v>
       </c>
       <c r="U30">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V30">
         <v>0.1</v>
       </c>
       <c r="W30">
-        <v>0.05769000000000001</v>
+        <v>0.06471</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>3.009181554634982</v>
+        <v>2.590225434875481</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09935455149899901</v>
+        <v>0.09949414516377859</v>
       </c>
       <c r="C31">
-        <v>423.9239784624776</v>
+        <v>415.8982605749497</v>
       </c>
       <c r="D31">
-        <v>549.1659784624776</v>
+        <v>547.7382605749497</v>
       </c>
       <c r="E31">
-        <v>115.342</v>
+        <v>121.94</v>
       </c>
       <c r="F31">
-        <v>191.342</v>
+        <v>197.94</v>
       </c>
       <c r="G31">
         <v>66.09999999999999</v>
@@ -3817,28 +3817,28 @@
         <v>35.635</v>
       </c>
       <c r="M31">
-        <v>13.7574898</v>
+        <v>14.231886</v>
       </c>
       <c r="N31">
-        <v>21.8775102</v>
+        <v>21.403114</v>
       </c>
       <c r="O31">
-        <v>2.18775102</v>
+        <v>2.1403114</v>
       </c>
       <c r="P31">
-        <v>19.68975918</v>
+        <v>19.2628026</v>
       </c>
       <c r="Q31">
-        <v>21.17975917999999</v>
+        <v>20.7528026</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1135051429563366</v>
+        <v>0.1144016359482551</v>
       </c>
       <c r="T31">
-        <v>1.357058864126733</v>
+        <v>1.37502786482872</v>
       </c>
       <c r="U31">
         <v>0.07190000000000001</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.590225434875481</v>
+        <v>2.503884587046299</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09949414516377859</v>
+        <v>0.1007218388285582</v>
       </c>
       <c r="C32">
-        <v>415.8982605749497</v>
+        <v>397.0564099172108</v>
       </c>
       <c r="D32">
-        <v>547.7382605749497</v>
+        <v>535.4944099172108</v>
       </c>
       <c r="E32">
-        <v>121.94</v>
+        <v>128.538</v>
       </c>
       <c r="F32">
-        <v>197.94</v>
+        <v>204.538</v>
       </c>
       <c r="G32">
         <v>66.09999999999999</v>
@@ -3899,45 +3899,45 @@
         <v>35.635</v>
       </c>
       <c r="M32">
-        <v>14.231886</v>
+        <v>15.5039804</v>
       </c>
       <c r="N32">
-        <v>21.403114</v>
+        <v>20.1310196</v>
       </c>
       <c r="O32">
-        <v>2.1403114</v>
+        <v>2.01310196</v>
       </c>
       <c r="P32">
-        <v>19.2628026</v>
+        <v>18.11791764</v>
       </c>
       <c r="Q32">
-        <v>20.7528026</v>
+        <v>19.60791764</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1144016359482551</v>
+        <v>0.1153241142442873</v>
       </c>
       <c r="T32">
-        <v>1.37502786482872</v>
+        <v>1.393517706130764</v>
       </c>
       <c r="U32">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V32">
         <v>0.1</v>
       </c>
       <c r="W32">
-        <v>0.06471</v>
+        <v>0.06822</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y32">
-        <v>2.503884587046299</v>
+        <v>2.298442018154254</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1007218388285582</v>
+        <v>0.1008965324933378</v>
       </c>
       <c r="C33">
-        <v>397.0564099172108</v>
+        <v>388.760526643908</v>
       </c>
       <c r="D33">
-        <v>535.4944099172108</v>
+        <v>533.7965266439079</v>
       </c>
       <c r="E33">
-        <v>128.538</v>
+        <v>135.136</v>
       </c>
       <c r="F33">
-        <v>204.538</v>
+        <v>211.136</v>
       </c>
       <c r="G33">
         <v>66.09999999999999</v>
@@ -3981,28 +3981,28 @@
         <v>35.635</v>
       </c>
       <c r="M33">
-        <v>15.5039804</v>
+        <v>16.0041088</v>
       </c>
       <c r="N33">
-        <v>20.1310196</v>
+        <v>19.6308912</v>
       </c>
       <c r="O33">
-        <v>2.01310196</v>
+        <v>1.96308912</v>
       </c>
       <c r="P33">
-        <v>18.11791764</v>
+        <v>17.66780208</v>
       </c>
       <c r="Q33">
-        <v>19.60791764</v>
+        <v>19.15780208</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1153241142442873</v>
+        <v>0.1162737242549086</v>
       </c>
       <c r="T33">
-        <v>1.393517706130764</v>
+        <v>1.412551366294634</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.298442018154254</v>
+        <v>2.226615705086934</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1008965324933378</v>
+        <v>0.1010712261581174</v>
       </c>
       <c r="C34">
-        <v>388.760526643908</v>
+        <v>380.4753762409244</v>
       </c>
       <c r="D34">
-        <v>533.7965266439079</v>
+        <v>532.1093762409245</v>
       </c>
       <c r="E34">
-        <v>135.136</v>
+        <v>141.734</v>
       </c>
       <c r="F34">
-        <v>211.136</v>
+        <v>217.734</v>
       </c>
       <c r="G34">
         <v>66.09999999999999</v>
@@ -4063,28 +4063,28 @@
         <v>35.635</v>
       </c>
       <c r="M34">
-        <v>16.0041088</v>
+        <v>16.5042372</v>
       </c>
       <c r="N34">
-        <v>19.6308912</v>
+        <v>19.1307628</v>
       </c>
       <c r="O34">
-        <v>1.96308912</v>
+        <v>1.91307628</v>
       </c>
       <c r="P34">
-        <v>17.66780208</v>
+        <v>17.21768652</v>
       </c>
       <c r="Q34">
-        <v>19.15780208</v>
+        <v>18.70768652</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1162737242549086</v>
+        <v>0.1172516808330111</v>
       </c>
       <c r="T34">
-        <v>1.412551366294634</v>
+        <v>1.432153195418619</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.226615705086934</v>
+        <v>2.159142501902481</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1010712261581174</v>
+        <v>0.101245919822897</v>
       </c>
       <c r="C35">
-        <v>380.4753762409244</v>
+        <v>372.2008572599781</v>
       </c>
       <c r="D35">
-        <v>532.1093762409245</v>
+        <v>530.4328572599781</v>
       </c>
       <c r="E35">
-        <v>141.734</v>
+        <v>148.332</v>
       </c>
       <c r="F35">
-        <v>217.734</v>
+        <v>224.332</v>
       </c>
       <c r="G35">
         <v>66.09999999999999</v>
@@ -4145,28 +4145,28 @@
         <v>35.635</v>
       </c>
       <c r="M35">
-        <v>16.5042372</v>
+        <v>17.0043656</v>
       </c>
       <c r="N35">
-        <v>19.1307628</v>
+        <v>18.6306344</v>
       </c>
       <c r="O35">
-        <v>1.91307628</v>
+        <v>1.86306344</v>
       </c>
       <c r="P35">
-        <v>17.21768652</v>
+        <v>16.76757096</v>
       </c>
       <c r="Q35">
-        <v>18.70768652</v>
+        <v>18.25757096</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1172516808330111</v>
+        <v>0.1182592724589349</v>
       </c>
       <c r="T35">
-        <v>1.432153195418619</v>
+        <v>1.452349019364543</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.159142501902481</v>
+        <v>2.095638310670055</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.101245919822897</v>
+        <v>0.1014206134876766</v>
       </c>
       <c r="C36">
-        <v>372.2008572599781</v>
+        <v>363.9368695273043</v>
       </c>
       <c r="D36">
-        <v>530.4328572599781</v>
+        <v>528.7668695273043</v>
       </c>
       <c r="E36">
-        <v>148.332</v>
+        <v>154.93</v>
       </c>
       <c r="F36">
-        <v>224.332</v>
+        <v>230.93</v>
       </c>
       <c r="G36">
         <v>66.09999999999999</v>
@@ -4227,28 +4227,28 @@
         <v>35.635</v>
       </c>
       <c r="M36">
-        <v>17.0043656</v>
+        <v>17.504494</v>
       </c>
       <c r="N36">
-        <v>18.6306344</v>
+        <v>18.130506</v>
       </c>
       <c r="O36">
-        <v>1.86306344</v>
+        <v>1.8130506</v>
       </c>
       <c r="P36">
-        <v>16.76757096</v>
+        <v>16.3174554</v>
       </c>
       <c r="Q36">
-        <v>18.25757096</v>
+        <v>17.80745539999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1182592724589349</v>
+        <v>0.1192978669041179</v>
       </c>
       <c r="T36">
-        <v>1.452349019364543</v>
+        <v>1.473166253278034</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.095638310670055</v>
+        <v>2.035762930365197</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1014206134876766</v>
+        <v>0.1061961071524563</v>
       </c>
       <c r="C37">
-        <v>363.9368695273043</v>
+        <v>315.529505403903</v>
       </c>
       <c r="D37">
-        <v>528.7668695273043</v>
+        <v>486.9575054039031</v>
       </c>
       <c r="E37">
-        <v>154.93</v>
+        <v>161.528</v>
       </c>
       <c r="F37">
-        <v>230.93</v>
+        <v>237.528</v>
       </c>
       <c r="G37">
         <v>66.09999999999999</v>
@@ -4309,45 +4309,45 @@
         <v>35.635</v>
       </c>
       <c r="M37">
-        <v>17.504494</v>
+        <v>21.37752</v>
       </c>
       <c r="N37">
-        <v>18.130506</v>
+        <v>14.25748</v>
       </c>
       <c r="O37">
-        <v>1.8130506</v>
+        <v>1.425748</v>
       </c>
       <c r="P37">
-        <v>16.3174554</v>
+        <v>12.831732</v>
       </c>
       <c r="Q37">
-        <v>17.80745539999999</v>
+        <v>14.321732</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1192978669041179</v>
+        <v>0.1203689174257129</v>
       </c>
       <c r="T37">
-        <v>1.473166253278034</v>
+        <v>1.494634025751321</v>
       </c>
       <c r="U37">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V37">
         <v>0.1</v>
       </c>
       <c r="W37">
-        <v>0.06822</v>
+        <v>0.081</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y37">
-        <v>2.035762930365197</v>
+        <v>1.666937979709527</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1061961071524563</v>
+        <v>0.1064986008172359</v>
       </c>
       <c r="C38">
-        <v>315.529505403903</v>
+        <v>306.504735125539</v>
       </c>
       <c r="D38">
-        <v>486.957505403903</v>
+        <v>484.530735125539</v>
       </c>
       <c r="E38">
-        <v>161.528</v>
+        <v>168.126</v>
       </c>
       <c r="F38">
-        <v>237.528</v>
+        <v>244.126</v>
       </c>
       <c r="G38">
         <v>66.09999999999999</v>
@@ -4391,28 +4391,28 @@
         <v>35.635</v>
       </c>
       <c r="M38">
-        <v>21.37752</v>
+        <v>21.97134</v>
       </c>
       <c r="N38">
-        <v>14.25748</v>
+        <v>13.66366</v>
       </c>
       <c r="O38">
-        <v>1.425748</v>
+        <v>1.366366</v>
       </c>
       <c r="P38">
-        <v>12.831732</v>
+        <v>12.297294</v>
       </c>
       <c r="Q38">
-        <v>14.321732</v>
+        <v>13.787294</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1203689174257129</v>
+        <v>0.121473969551168</v>
       </c>
       <c r="T38">
-        <v>1.494634025751321</v>
+        <v>1.516783314811062</v>
       </c>
       <c r="U38">
         <v>0.09</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>1.666937979709527</v>
+        <v>1.621885601879539</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1064986008172359</v>
+        <v>0.1068010944820155</v>
       </c>
       <c r="C39">
-        <v>306.504735125539</v>
+        <v>297.5040326984587</v>
       </c>
       <c r="D39">
-        <v>484.530735125539</v>
+        <v>482.1280326984587</v>
       </c>
       <c r="E39">
-        <v>168.126</v>
+        <v>174.724</v>
       </c>
       <c r="F39">
-        <v>244.126</v>
+        <v>250.724</v>
       </c>
       <c r="G39">
         <v>66.09999999999999</v>
@@ -4473,28 +4473,28 @@
         <v>35.635</v>
       </c>
       <c r="M39">
-        <v>21.97134</v>
+        <v>22.56516</v>
       </c>
       <c r="N39">
-        <v>13.66366</v>
+        <v>13.06984</v>
       </c>
       <c r="O39">
-        <v>1.366366</v>
+        <v>1.306984</v>
       </c>
       <c r="P39">
-        <v>12.297294</v>
+        <v>11.762856</v>
       </c>
       <c r="Q39">
-        <v>13.787294</v>
+        <v>13.252856</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.121473969551168</v>
+        <v>0.1226146685193798</v>
       </c>
       <c r="T39">
-        <v>1.516783314811062</v>
+        <v>1.539647097066279</v>
       </c>
       <c r="U39">
         <v>0.09</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>1.621885601879539</v>
+        <v>1.579204401830078</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1068010944820155</v>
+        <v>0.1071035881467951</v>
       </c>
       <c r="C40">
-        <v>297.5040326984587</v>
+        <v>288.5270418446981</v>
       </c>
       <c r="D40">
-        <v>482.1280326984587</v>
+        <v>479.7490418446982</v>
       </c>
       <c r="E40">
-        <v>174.724</v>
+        <v>181.322</v>
       </c>
       <c r="F40">
-        <v>250.724</v>
+        <v>257.322</v>
       </c>
       <c r="G40">
         <v>66.09999999999999</v>
@@ -4555,28 +4555,28 @@
         <v>35.635</v>
       </c>
       <c r="M40">
-        <v>22.56516</v>
+        <v>23.15898</v>
       </c>
       <c r="N40">
-        <v>13.06984</v>
+        <v>12.47602</v>
       </c>
       <c r="O40">
-        <v>1.306984</v>
+        <v>1.247602</v>
       </c>
       <c r="P40">
-        <v>11.762856</v>
+        <v>11.228418</v>
       </c>
       <c r="Q40">
-        <v>13.252856</v>
+        <v>12.718418</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1226146685193798</v>
+        <v>0.1237927674537624</v>
       </c>
       <c r="T40">
-        <v>1.539647097066279</v>
+        <v>1.563260511526584</v>
       </c>
       <c r="U40">
         <v>0.09</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>1.579204401830078</v>
+        <v>1.538711981270332</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1071035881467951</v>
+        <v>0.1074060818115747</v>
       </c>
       <c r="C41">
-        <v>288.5270418446981</v>
+        <v>279.5734132837717</v>
       </c>
       <c r="D41">
-        <v>479.7490418446982</v>
+        <v>477.3934132837717</v>
       </c>
       <c r="E41">
-        <v>181.322</v>
+        <v>187.92</v>
       </c>
       <c r="F41">
-        <v>257.322</v>
+        <v>263.92</v>
       </c>
       <c r="G41">
         <v>66.09999999999999</v>
@@ -4637,28 +4637,28 @@
         <v>35.635</v>
       </c>
       <c r="M41">
-        <v>23.15898</v>
+        <v>23.7528</v>
       </c>
       <c r="N41">
-        <v>12.47602</v>
+        <v>11.8822</v>
       </c>
       <c r="O41">
-        <v>1.247602</v>
+        <v>1.18822</v>
       </c>
       <c r="P41">
-        <v>11.228418</v>
+        <v>10.69398</v>
       </c>
       <c r="Q41">
-        <v>12.718418</v>
+        <v>12.18398</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1237927674537624</v>
+        <v>0.1250101363526245</v>
       </c>
       <c r="T41">
-        <v>1.563260511526584</v>
+        <v>1.587661039802233</v>
       </c>
       <c r="U41">
         <v>0.09</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>1.538711981270332</v>
+        <v>1.500244181738574</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1074060818115747</v>
+        <v>0.1294940819907573</v>
       </c>
       <c r="C42">
-        <v>279.5734132837717</v>
+        <v>146.9848348899847</v>
       </c>
       <c r="D42">
-        <v>477.3934132837717</v>
+        <v>351.4028348899847</v>
       </c>
       <c r="E42">
-        <v>187.92</v>
+        <v>194.518</v>
       </c>
       <c r="F42">
-        <v>263.92</v>
+        <v>270.518</v>
       </c>
       <c r="G42">
         <v>66.09999999999999</v>
@@ -4719,45 +4719,45 @@
         <v>35.635</v>
       </c>
       <c r="M42">
-        <v>23.7528</v>
+        <v>39.71204240000001</v>
       </c>
       <c r="N42">
-        <v>11.8822</v>
+        <v>-4.077042400000011</v>
       </c>
       <c r="O42">
-        <v>1.18822</v>
+        <v>-0.4077042400000011</v>
       </c>
       <c r="P42">
-        <v>10.69398</v>
+        <v>-3.669338160000009</v>
       </c>
       <c r="Q42">
-        <v>12.18398</v>
+        <v>-2.179338160000009</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1250101363526245</v>
+        <v>0.1266219678729088</v>
       </c>
       <c r="T42">
-        <v>1.587661039802233</v>
+        <v>1.619968042735397</v>
       </c>
       <c r="U42">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V42">
-        <v>0.1</v>
+        <v>0.08973348598157216</v>
       </c>
       <c r="W42">
-        <v>0.081</v>
+        <v>0.1336271242579052</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y42">
-        <v>1.500244181738574</v>
+        <v>0.8973348598157216</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1294940819907573</v>
+        <v>0.1305040819907573</v>
       </c>
       <c r="C43">
-        <v>146.9848348899847</v>
+        <v>136.1967550863027</v>
       </c>
       <c r="D43">
-        <v>351.4028348899847</v>
+        <v>347.2127550863027</v>
       </c>
       <c r="E43">
-        <v>194.518</v>
+        <v>201.116</v>
       </c>
       <c r="F43">
-        <v>270.518</v>
+        <v>277.116</v>
       </c>
       <c r="G43">
         <v>66.09999999999999</v>
@@ -4801,37 +4801,37 @@
         <v>35.635</v>
       </c>
       <c r="M43">
-        <v>39.71204240000001</v>
+        <v>40.6806288</v>
       </c>
       <c r="N43">
-        <v>-4.077042400000011</v>
+        <v>-5.045628800000003</v>
       </c>
       <c r="O43">
-        <v>-0.4077042400000011</v>
+        <v>-0.5045628800000003</v>
       </c>
       <c r="P43">
-        <v>-3.669338160000009</v>
+        <v>-4.541065920000003</v>
       </c>
       <c r="Q43">
-        <v>-2.179338160000009</v>
+        <v>-3.051065920000003</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1266219678729088</v>
+        <v>0.1280154500776141</v>
       </c>
       <c r="T43">
-        <v>1.619968042735397</v>
+        <v>1.647898526230835</v>
       </c>
       <c r="U43">
         <v>0.1468</v>
       </c>
       <c r="V43">
-        <v>0.08973348598157216</v>
+        <v>0.08759697441058237</v>
       </c>
       <c r="W43">
-        <v>0.1336271242579052</v>
+        <v>0.1339407641565265</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.8973348598157216</v>
+        <v>0.8759697441058236</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1305040819907573</v>
+        <v>0.1315140819907573</v>
       </c>
       <c r="C44">
-        <v>136.1967550863028</v>
+        <v>125.5074217313591</v>
       </c>
       <c r="D44">
-        <v>347.2127550863028</v>
+        <v>343.1214217313591</v>
       </c>
       <c r="E44">
-        <v>201.116</v>
+        <v>207.714</v>
       </c>
       <c r="F44">
-        <v>277.116</v>
+        <v>283.714</v>
       </c>
       <c r="G44">
         <v>66.09999999999999</v>
@@ -4883,37 +4883,37 @@
         <v>35.635</v>
       </c>
       <c r="M44">
-        <v>40.6806288</v>
+        <v>41.6492152</v>
       </c>
       <c r="N44">
-        <v>-5.045628800000003</v>
+        <v>-6.014215200000002</v>
       </c>
       <c r="O44">
-        <v>-0.5045628800000003</v>
+        <v>-0.6014215200000003</v>
       </c>
       <c r="P44">
-        <v>-4.541065920000003</v>
+        <v>-5.412793680000002</v>
       </c>
       <c r="Q44">
-        <v>-3.051065920000003</v>
+        <v>-3.922793680000002</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1280154500776141</v>
+        <v>0.1294578263947652</v>
       </c>
       <c r="T44">
-        <v>1.647898526230834</v>
+        <v>1.676809026691024</v>
       </c>
       <c r="U44">
         <v>0.1468</v>
       </c>
       <c r="V44">
-        <v>0.08759697441058237</v>
+        <v>0.08555983547080137</v>
       </c>
       <c r="W44">
-        <v>0.1339407641565265</v>
+        <v>0.1342398161528864</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.8759697441058236</v>
+        <v>0.8555983547080137</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1315140819907573</v>
+        <v>0.1325240819907573</v>
       </c>
       <c r="C45">
-        <v>125.5074217313591</v>
+        <v>114.9133847829875</v>
       </c>
       <c r="D45">
-        <v>343.1214217313591</v>
+        <v>339.1253847829875</v>
       </c>
       <c r="E45">
-        <v>207.714</v>
+        <v>214.312</v>
       </c>
       <c r="F45">
-        <v>283.714</v>
+        <v>290.312</v>
       </c>
       <c r="G45">
         <v>66.09999999999999</v>
@@ -4965,37 +4965,37 @@
         <v>35.635</v>
       </c>
       <c r="M45">
-        <v>41.6492152</v>
+        <v>42.6178016</v>
       </c>
       <c r="N45">
-        <v>-6.014215200000002</v>
+        <v>-6.982801600000002</v>
       </c>
       <c r="O45">
-        <v>-0.6014215200000003</v>
+        <v>-0.6982801600000003</v>
       </c>
       <c r="P45">
-        <v>-5.412793680000002</v>
+        <v>-6.284521440000002</v>
       </c>
       <c r="Q45">
-        <v>-3.922793680000002</v>
+        <v>-4.794521440000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1294578263947652</v>
+        <v>0.1309517161518146</v>
       </c>
       <c r="T45">
-        <v>1.676809026691024</v>
+        <v>1.706752045024793</v>
       </c>
       <c r="U45">
         <v>0.1468</v>
       </c>
       <c r="V45">
-        <v>0.08555983547080137</v>
+        <v>0.08361529375555589</v>
       </c>
       <c r="W45">
-        <v>0.1342398161528864</v>
+        <v>0.1345252748766844</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.8555983547080137</v>
+        <v>0.8361529375555589</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1325240819907573</v>
+        <v>0.1335340819907573</v>
       </c>
       <c r="C46">
-        <v>114.9133847829875</v>
+        <v>104.4113530673893</v>
       </c>
       <c r="D46">
-        <v>339.1253847829875</v>
+        <v>335.2213530673893</v>
       </c>
       <c r="E46">
-        <v>214.312</v>
+        <v>220.91</v>
       </c>
       <c r="F46">
-        <v>290.312</v>
+        <v>296.91</v>
       </c>
       <c r="G46">
         <v>66.09999999999999</v>
@@ -5047,37 +5047,37 @@
         <v>35.635</v>
       </c>
       <c r="M46">
-        <v>42.6178016</v>
+        <v>43.586388</v>
       </c>
       <c r="N46">
-        <v>-6.982801600000002</v>
+        <v>-7.951388000000001</v>
       </c>
       <c r="O46">
-        <v>-0.6982801600000003</v>
+        <v>-0.7951388000000001</v>
       </c>
       <c r="P46">
-        <v>-6.284521440000002</v>
+        <v>-7.156249200000001</v>
       </c>
       <c r="Q46">
-        <v>-4.794521440000001</v>
+        <v>-5.666249200000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1309517161518146</v>
+        <v>0.1324999291727567</v>
       </c>
       <c r="T46">
-        <v>1.706752045024793</v>
+        <v>1.73778390038888</v>
       </c>
       <c r="U46">
         <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.08361529375555589</v>
+        <v>0.08175717611654354</v>
       </c>
       <c r="W46">
-        <v>0.1345252748766844</v>
+        <v>0.1347980465460914</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.8361529375555589</v>
+        <v>0.8175717611654354</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1335340819907573</v>
+        <v>0.1598738937709874</v>
       </c>
       <c r="C47">
-        <v>104.4113530673893</v>
+        <v>20.41030270570553</v>
       </c>
       <c r="D47">
-        <v>335.2213530673893</v>
+        <v>257.8183027057055</v>
       </c>
       <c r="E47">
-        <v>220.91</v>
+        <v>227.508</v>
       </c>
       <c r="F47">
-        <v>296.91</v>
+        <v>303.508</v>
       </c>
       <c r="G47">
         <v>66.09999999999999</v>
@@ -5129,45 +5129,45 @@
         <v>35.635</v>
       </c>
       <c r="M47">
-        <v>43.586388</v>
+        <v>60.9444064</v>
       </c>
       <c r="N47">
-        <v>-7.951388000000001</v>
+        <v>-25.3094064</v>
       </c>
       <c r="O47">
-        <v>-0.7951388000000001</v>
+        <v>-2.53094064</v>
       </c>
       <c r="P47">
-        <v>-7.156249200000001</v>
+        <v>-22.77846576</v>
       </c>
       <c r="Q47">
-        <v>-5.666249200000001</v>
+        <v>-21.28846576</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1324999291727567</v>
+        <v>0.1350125422689746</v>
       </c>
       <c r="T47">
-        <v>1.73778390038888</v>
+        <v>1.788145862943813</v>
       </c>
       <c r="U47">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.08175717611654354</v>
+        <v>0.05847132182421257</v>
       </c>
       <c r="W47">
-        <v>0.1347980465460914</v>
+        <v>0.1890589585776981</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y47">
-        <v>0.8175717611654354</v>
+        <v>0.5847132182421256</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1598738937709874</v>
+        <v>0.1614238937709874</v>
       </c>
       <c r="C48">
-        <v>20.41030270570553</v>
+        <v>10.35611077027943</v>
       </c>
       <c r="D48">
-        <v>257.8183027057055</v>
+        <v>254.3621107702795</v>
       </c>
       <c r="E48">
-        <v>227.508</v>
+        <v>234.106</v>
       </c>
       <c r="F48">
-        <v>303.508</v>
+        <v>310.106</v>
       </c>
       <c r="G48">
         <v>66.09999999999999</v>
@@ -5211,37 +5211,37 @@
         <v>35.635</v>
       </c>
       <c r="M48">
-        <v>60.9444064</v>
+        <v>62.2692848</v>
       </c>
       <c r="N48">
-        <v>-25.3094064</v>
+        <v>-26.6342848</v>
       </c>
       <c r="O48">
-        <v>-2.53094064</v>
+        <v>-2.66342848</v>
       </c>
       <c r="P48">
-        <v>-22.77846576</v>
+        <v>-23.97085632</v>
       </c>
       <c r="Q48">
-        <v>-21.28846576</v>
+        <v>-22.48085632</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1350125422689746</v>
+        <v>0.1366957977834835</v>
       </c>
       <c r="T48">
-        <v>1.788145862943813</v>
+        <v>1.821884464131432</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.05847132182421257</v>
+        <v>0.05722725114710166</v>
       </c>
       <c r="W48">
-        <v>0.1890589585776981</v>
+        <v>0.189308767969662</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.5847132182421256</v>
+        <v>0.5722725114710165</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1614238937709874</v>
+        <v>0.1629738937709874</v>
       </c>
       <c r="C49">
-        <v>10.35611077027943</v>
+        <v>0.3933572487782726</v>
       </c>
       <c r="D49">
-        <v>254.3621107702795</v>
+        <v>250.9973572487783</v>
       </c>
       <c r="E49">
-        <v>234.106</v>
+        <v>240.704</v>
       </c>
       <c r="F49">
-        <v>310.106</v>
+        <v>316.704</v>
       </c>
       <c r="G49">
         <v>66.09999999999999</v>
@@ -5293,37 +5293,37 @@
         <v>35.635</v>
       </c>
       <c r="M49">
-        <v>62.2692848</v>
+        <v>63.5941632</v>
       </c>
       <c r="N49">
-        <v>-26.6342848</v>
+        <v>-27.95916320000001</v>
       </c>
       <c r="O49">
-        <v>-2.66342848</v>
+        <v>-2.795916320000001</v>
       </c>
       <c r="P49">
-        <v>-23.97085632</v>
+        <v>-25.16324688000001</v>
       </c>
       <c r="Q49">
-        <v>-22.48085632</v>
+        <v>-23.67324688000001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1366957977834835</v>
+        <v>0.1384437938947044</v>
       </c>
       <c r="T49">
-        <v>1.821884464131432</v>
+        <v>1.856920703826268</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.05722725114710166</v>
+        <v>0.05603501674820371</v>
       </c>
       <c r="W49">
-        <v>0.189308767969662</v>
+        <v>0.1895481686369607</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.5722725114710165</v>
+        <v>0.560350167482037</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1629738937709874</v>
+        <v>0.1645238937709874</v>
       </c>
       <c r="C50">
-        <v>0.3933572487783294</v>
+        <v>-9.481539181910307</v>
       </c>
       <c r="D50">
-        <v>250.9973572487783</v>
+        <v>247.7204608180897</v>
       </c>
       <c r="E50">
-        <v>240.704</v>
+        <v>247.302</v>
       </c>
       <c r="F50">
-        <v>316.704</v>
+        <v>323.302</v>
       </c>
       <c r="G50">
         <v>66.09999999999999</v>
@@ -5375,37 +5375,37 @@
         <v>35.635</v>
       </c>
       <c r="M50">
-        <v>63.59416319999999</v>
+        <v>64.9190416</v>
       </c>
       <c r="N50">
-        <v>-27.95916319999999</v>
+        <v>-29.2840416</v>
       </c>
       <c r="O50">
-        <v>-2.795916319999999</v>
+        <v>-2.92840416</v>
       </c>
       <c r="P50">
-        <v>-25.16324687999999</v>
+        <v>-26.35563744</v>
       </c>
       <c r="Q50">
-        <v>-23.67324687999999</v>
+        <v>-24.86563744</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1384437938947044</v>
+        <v>0.1402603388730319</v>
       </c>
       <c r="T50">
-        <v>1.856920703826267</v>
+        <v>1.893330913705214</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.05603501674820371</v>
+        <v>0.05489144497783221</v>
       </c>
       <c r="W50">
-        <v>0.1895481686369607</v>
+        <v>0.1897777978484513</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.5603501674820371</v>
+        <v>0.548914449778322</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1645238937709874</v>
+        <v>0.1660738937709874</v>
       </c>
       <c r="C51">
-        <v>-9.481539181910307</v>
+        <v>-19.27197523124244</v>
       </c>
       <c r="D51">
-        <v>247.7204608180897</v>
+        <v>244.5280247687576</v>
       </c>
       <c r="E51">
-        <v>247.302</v>
+        <v>253.9</v>
       </c>
       <c r="F51">
-        <v>323.302</v>
+        <v>329.9</v>
       </c>
       <c r="G51">
         <v>66.09999999999999</v>
@@ -5457,37 +5457,37 @@
         <v>35.635</v>
       </c>
       <c r="M51">
-        <v>64.9190416</v>
+        <v>66.24392</v>
       </c>
       <c r="N51">
-        <v>-29.2840416</v>
+        <v>-30.60892</v>
       </c>
       <c r="O51">
-        <v>-2.92840416</v>
+        <v>-3.060892000000001</v>
       </c>
       <c r="P51">
-        <v>-26.35563744</v>
+        <v>-27.548028</v>
       </c>
       <c r="Q51">
-        <v>-24.86563744</v>
+        <v>-26.058028</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1402603388730319</v>
+        <v>0.1421495456504925</v>
       </c>
       <c r="T51">
-        <v>1.893330913705214</v>
+        <v>1.931197531979318</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.05489144497783221</v>
+        <v>0.05379361607827556</v>
       </c>
       <c r="W51">
-        <v>0.1897777978484513</v>
+        <v>0.1899982418914823</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.548914449778322</v>
+        <v>0.5379361607827555</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1660738937709874</v>
+        <v>0.1676238937709874</v>
       </c>
       <c r="C52">
-        <v>-19.27197523124244</v>
+        <v>-28.98117473947747</v>
       </c>
       <c r="D52">
-        <v>244.5280247687576</v>
+        <v>241.4168252605226</v>
       </c>
       <c r="E52">
-        <v>253.9</v>
+        <v>260.498</v>
       </c>
       <c r="F52">
-        <v>329.9</v>
+        <v>336.498</v>
       </c>
       <c r="G52">
         <v>66.09999999999999</v>
@@ -5539,37 +5539,37 @@
         <v>35.635</v>
       </c>
       <c r="M52">
-        <v>66.24392</v>
+        <v>67.56879840000001</v>
       </c>
       <c r="N52">
-        <v>-30.60892</v>
+        <v>-31.93379840000001</v>
       </c>
       <c r="O52">
-        <v>-3.060892000000001</v>
+        <v>-3.193379840000001</v>
       </c>
       <c r="P52">
-        <v>-27.548028</v>
+        <v>-28.74041856000001</v>
       </c>
       <c r="Q52">
-        <v>-26.058028</v>
+        <v>-27.25041856000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1421495456504925</v>
+        <v>0.1441158629086658</v>
       </c>
       <c r="T52">
-        <v>1.931197531979318</v>
+        <v>1.970609726509508</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.05379361607827556</v>
+        <v>0.05273883929242701</v>
       </c>
       <c r="W52">
-        <v>0.1899982418914823</v>
+        <v>0.1902100410700807</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.5379361607827555</v>
+        <v>0.5273883929242702</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1676238937709874</v>
+        <v>0.1691738937709874</v>
       </c>
       <c r="C53">
-        <v>-28.98117473947747</v>
+        <v>-38.61219953683371</v>
       </c>
       <c r="D53">
-        <v>241.4168252605226</v>
+        <v>238.3838004631663</v>
       </c>
       <c r="E53">
-        <v>260.498</v>
+        <v>267.096</v>
       </c>
       <c r="F53">
-        <v>336.498</v>
+        <v>343.096</v>
       </c>
       <c r="G53">
         <v>66.09999999999999</v>
@@ -5621,37 +5621,37 @@
         <v>35.635</v>
       </c>
       <c r="M53">
-        <v>67.56879840000001</v>
+        <v>68.89367680000001</v>
       </c>
       <c r="N53">
-        <v>-31.93379840000001</v>
+        <v>-33.25867680000001</v>
       </c>
       <c r="O53">
-        <v>-3.193379840000001</v>
+        <v>-3.325867680000001</v>
       </c>
       <c r="P53">
-        <v>-28.74041856000001</v>
+        <v>-29.93280912000001</v>
       </c>
       <c r="Q53">
-        <v>-27.25041856000001</v>
+        <v>-28.44280912000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1441158629086658</v>
+        <v>0.1461641100525964</v>
       </c>
       <c r="T53">
-        <v>1.970609726509508</v>
+        <v>2.01166409581179</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.05273883929242701</v>
+        <v>0.05172463084449572</v>
       </c>
       <c r="W53">
-        <v>0.1902100410700807</v>
+        <v>0.1904136941264253</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.5273883929242702</v>
+        <v>0.5172463084449572</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1691738937709874</v>
+        <v>0.1707238937709874</v>
       </c>
       <c r="C54">
-        <v>-38.61219953683371</v>
+        <v>-48.1679594942305</v>
       </c>
       <c r="D54">
-        <v>238.3838004631663</v>
+        <v>235.4260405057695</v>
       </c>
       <c r="E54">
-        <v>267.096</v>
+        <v>273.694</v>
       </c>
       <c r="F54">
-        <v>343.096</v>
+        <v>349.694</v>
       </c>
       <c r="G54">
         <v>66.09999999999999</v>
@@ -5703,37 +5703,37 @@
         <v>35.635</v>
       </c>
       <c r="M54">
-        <v>68.89367680000001</v>
+        <v>70.21855520000001</v>
       </c>
       <c r="N54">
-        <v>-33.25867680000001</v>
+        <v>-34.58355520000001</v>
       </c>
       <c r="O54">
-        <v>-3.325867680000001</v>
+        <v>-3.458355520000001</v>
       </c>
       <c r="P54">
-        <v>-29.93280912000001</v>
+        <v>-31.12519968000001</v>
       </c>
       <c r="Q54">
-        <v>-28.44280912000001</v>
+        <v>-29.63519968000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1461641100525964</v>
+        <v>0.1482995166494601</v>
       </c>
       <c r="T54">
-        <v>2.01166409581179</v>
+        <v>2.054465459552466</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.05172463084449572</v>
+        <v>0.0507486944134675</v>
       </c>
       <c r="W54">
-        <v>0.1904136941264253</v>
+        <v>0.1906096621617757</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5172463084449572</v>
+        <v>0.507486944134675</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1707238937709874</v>
+        <v>0.1913715387405805</v>
       </c>
       <c r="C55">
-        <v>-48.1679594942305</v>
+        <v>-88.15842991128653</v>
       </c>
       <c r="D55">
-        <v>235.4260405057695</v>
+        <v>202.0335700887134</v>
       </c>
       <c r="E55">
-        <v>273.694</v>
+        <v>280.292</v>
       </c>
       <c r="F55">
-        <v>349.694</v>
+        <v>356.292</v>
       </c>
       <c r="G55">
         <v>66.09999999999999</v>
@@ -5785,45 +5785,45 @@
         <v>35.635</v>
       </c>
       <c r="M55">
-        <v>70.21855520000001</v>
+        <v>84.0136536</v>
       </c>
       <c r="N55">
-        <v>-34.58355520000001</v>
+        <v>-48.3786536</v>
       </c>
       <c r="O55">
-        <v>-3.458355520000001</v>
+        <v>-4.83786536</v>
       </c>
       <c r="P55">
-        <v>-31.12519968000001</v>
+        <v>-43.54078824</v>
       </c>
       <c r="Q55">
-        <v>-29.63519968000001</v>
+        <v>-42.05078824</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1482995166494601</v>
+        <v>0.1509574299887811</v>
       </c>
       <c r="T55">
-        <v>2.054465459552466</v>
+        <v>2.107739770774767</v>
       </c>
       <c r="U55">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.0507486944134675</v>
+        <v>0.04241572467454266</v>
       </c>
       <c r="W55">
-        <v>0.1906096621617757</v>
+        <v>0.2257983721217428</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y55">
-        <v>0.507486944134675</v>
+        <v>0.4241572467454267</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1913715387405805</v>
+        <v>0.1932715387405805</v>
       </c>
       <c r="C56">
-        <v>-88.15842991128653</v>
+        <v>-97.35939850066165</v>
       </c>
       <c r="D56">
-        <v>202.0335700887134</v>
+        <v>199.4306014993383</v>
       </c>
       <c r="E56">
-        <v>280.292</v>
+        <v>286.89</v>
       </c>
       <c r="F56">
-        <v>356.292</v>
+        <v>362.89</v>
       </c>
       <c r="G56">
         <v>66.09999999999999</v>
@@ -5867,37 +5867,37 @@
         <v>35.635</v>
       </c>
       <c r="M56">
-        <v>84.0136536</v>
+        <v>85.569462</v>
       </c>
       <c r="N56">
-        <v>-48.3786536</v>
+        <v>-49.934462</v>
       </c>
       <c r="O56">
-        <v>-4.83786536</v>
+        <v>-4.993446200000001</v>
       </c>
       <c r="P56">
-        <v>-43.54078824</v>
+        <v>-44.9410158</v>
       </c>
       <c r="Q56">
-        <v>-42.05078824</v>
+        <v>-43.4510158</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1509574299887811</v>
+        <v>0.1532942617663096</v>
       </c>
       <c r="T56">
-        <v>2.107739770774767</v>
+        <v>2.154578432347539</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.04241572467454266</v>
+        <v>0.04164452968046007</v>
       </c>
       <c r="W56">
-        <v>0.2257983721217428</v>
+        <v>0.2259802199013475</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.4241572467454267</v>
+        <v>0.4164452968046006</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1932715387405805</v>
+        <v>0.1951715387405805</v>
       </c>
       <c r="C57">
-        <v>-97.35939850066165</v>
+        <v>-106.4941477772882</v>
       </c>
       <c r="D57">
-        <v>199.4306014993383</v>
+        <v>196.8938522227118</v>
       </c>
       <c r="E57">
-        <v>286.89</v>
+        <v>293.488</v>
       </c>
       <c r="F57">
-        <v>362.89</v>
+        <v>369.488</v>
       </c>
       <c r="G57">
         <v>66.09999999999999</v>
@@ -5949,37 +5949,37 @@
         <v>35.635</v>
       </c>
       <c r="M57">
-        <v>85.569462</v>
+        <v>87.12527040000001</v>
       </c>
       <c r="N57">
-        <v>-49.934462</v>
+        <v>-51.49027040000001</v>
       </c>
       <c r="O57">
-        <v>-4.993446200000001</v>
+        <v>-5.149027040000001</v>
       </c>
       <c r="P57">
-        <v>-44.9410158</v>
+        <v>-46.34124336000001</v>
       </c>
       <c r="Q57">
-        <v>-43.4510158</v>
+        <v>-44.85124336000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1532942617663096</v>
+        <v>0.1557373131700894</v>
       </c>
       <c r="T57">
-        <v>2.154578432347539</v>
+        <v>2.203546123991802</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.04164452968046007</v>
+        <v>0.04090087736473757</v>
       </c>
       <c r="W57">
-        <v>0.2259802199013475</v>
+        <v>0.2261555731173949</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.4164452968046006</v>
+        <v>0.4090087736473756</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1951715387405805</v>
+        <v>0.1970715387405805</v>
       </c>
       <c r="C58">
-        <v>-106.4941477772882</v>
+        <v>-115.5651729235763</v>
       </c>
       <c r="D58">
-        <v>196.8938522227118</v>
+        <v>194.4208270764237</v>
       </c>
       <c r="E58">
-        <v>293.488</v>
+        <v>300.086</v>
       </c>
       <c r="F58">
-        <v>369.488</v>
+        <v>376.086</v>
       </c>
       <c r="G58">
         <v>66.09999999999999</v>
@@ -6031,37 +6031,37 @@
         <v>35.635</v>
       </c>
       <c r="M58">
-        <v>87.12527040000001</v>
+        <v>88.68107880000001</v>
       </c>
       <c r="N58">
-        <v>-51.49027040000001</v>
+        <v>-53.04607880000001</v>
       </c>
       <c r="O58">
-        <v>-5.149027040000001</v>
+        <v>-5.304607880000002</v>
       </c>
       <c r="P58">
-        <v>-46.34124336000001</v>
+        <v>-47.74147092000001</v>
       </c>
       <c r="Q58">
-        <v>-44.85124336000001</v>
+        <v>-46.25147092000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1557373131700894</v>
+        <v>0.1582939948717194</v>
       </c>
       <c r="T58">
-        <v>2.203546123991802</v>
+        <v>2.254791382689286</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.04090087736473757</v>
+        <v>0.04018331811272462</v>
       </c>
       <c r="W58">
-        <v>0.2261555731173949</v>
+        <v>0.2263247735890196</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.4090087736473756</v>
+        <v>0.4018331811272462</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1970715387405805</v>
+        <v>0.1989715387405805</v>
       </c>
       <c r="C59">
-        <v>-115.5651729235763</v>
+        <v>-124.5748453170413</v>
       </c>
       <c r="D59">
-        <v>194.4208270764237</v>
+        <v>192.0091546829588</v>
       </c>
       <c r="E59">
-        <v>300.086</v>
+        <v>306.684</v>
       </c>
       <c r="F59">
-        <v>376.086</v>
+        <v>382.684</v>
       </c>
       <c r="G59">
         <v>66.09999999999999</v>
@@ -6113,37 +6113,37 @@
         <v>35.635</v>
       </c>
       <c r="M59">
-        <v>88.68107880000001</v>
+        <v>90.23688720000001</v>
       </c>
       <c r="N59">
-        <v>-53.04607880000001</v>
+        <v>-54.60188720000001</v>
       </c>
       <c r="O59">
-        <v>-5.304607880000002</v>
+        <v>-5.460188720000001</v>
       </c>
       <c r="P59">
-        <v>-47.74147092000001</v>
+        <v>-49.14169848000002</v>
       </c>
       <c r="Q59">
-        <v>-46.25147092000001</v>
+        <v>-47.65169848000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1582939948717194</v>
+        <v>0.160972423321046</v>
       </c>
       <c r="T59">
-        <v>2.254791382689286</v>
+        <v>2.308476891800935</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.04018331811272462</v>
+        <v>0.03949050228319489</v>
       </c>
       <c r="W59">
-        <v>0.2263247735890196</v>
+        <v>0.2264881395616227</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.4018331811272462</v>
+        <v>0.3949050228319488</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1989715387405805</v>
+        <v>0.2008715387405805</v>
       </c>
       <c r="C60">
-        <v>-124.5748453170412</v>
+        <v>-133.5254201148441</v>
       </c>
       <c r="D60">
-        <v>192.0091546829588</v>
+        <v>189.6565798851558</v>
       </c>
       <c r="E60">
-        <v>306.684</v>
+        <v>313.2819999999999</v>
       </c>
       <c r="F60">
-        <v>382.684</v>
+        <v>389.2819999999999</v>
       </c>
       <c r="G60">
         <v>66.09999999999999</v>
@@ -6195,37 +6195,37 @@
         <v>35.635</v>
       </c>
       <c r="M60">
-        <v>90.2368872</v>
+        <v>91.79269559999999</v>
       </c>
       <c r="N60">
-        <v>-54.6018872</v>
+        <v>-56.15769559999999</v>
       </c>
       <c r="O60">
-        <v>-5.460188720000001</v>
+        <v>-5.615769559999999</v>
       </c>
       <c r="P60">
-        <v>-49.14169848</v>
+        <v>-50.54192603999999</v>
       </c>
       <c r="Q60">
-        <v>-47.65169848</v>
+        <v>-49.05192603999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.160972423321046</v>
+        <v>0.1637815068166813</v>
       </c>
       <c r="T60">
-        <v>2.308476891800935</v>
+        <v>2.364781206235104</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.03949050228319489</v>
+        <v>0.03882117173602211</v>
       </c>
       <c r="W60">
-        <v>0.2264881395616227</v>
+        <v>0.226645967704646</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3949050228319489</v>
+        <v>0.388211717360221</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2008715387405805</v>
+        <v>0.2027715387405804</v>
       </c>
       <c r="C61">
-        <v>-133.5254201148441</v>
+        <v>-142.4190432875094</v>
       </c>
       <c r="D61">
-        <v>189.6565798851558</v>
+        <v>187.3609567124905</v>
       </c>
       <c r="E61">
-        <v>313.2819999999999</v>
+        <v>319.8799999999999</v>
       </c>
       <c r="F61">
-        <v>389.2819999999999</v>
+        <v>395.8799999999999</v>
       </c>
       <c r="G61">
         <v>66.09999999999999</v>
@@ -6277,37 +6277,37 @@
         <v>35.635</v>
       </c>
       <c r="M61">
-        <v>91.79269559999999</v>
+        <v>93.34850399999999</v>
       </c>
       <c r="N61">
-        <v>-56.15769559999999</v>
+        <v>-57.71350399999999</v>
       </c>
       <c r="O61">
-        <v>-5.615769559999999</v>
+        <v>-5.771350399999999</v>
       </c>
       <c r="P61">
-        <v>-50.54192603999999</v>
+        <v>-51.9421536</v>
       </c>
       <c r="Q61">
-        <v>-49.05192603999999</v>
+        <v>-50.4521536</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1637815068166813</v>
+        <v>0.1667310444870983</v>
       </c>
       <c r="T61">
-        <v>2.364781206235104</v>
+        <v>2.423900736390981</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.03882117173602211</v>
+        <v>0.0381741522070884</v>
       </c>
       <c r="W61">
-        <v>0.226645967704646</v>
+        <v>0.2267985349095686</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.388211717360221</v>
+        <v>0.381741522070884</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2027715387405804</v>
+        <v>0.2046715387405805</v>
       </c>
       <c r="C62">
-        <v>-142.4190432875094</v>
+        <v>-151.2577581479289</v>
       </c>
       <c r="D62">
-        <v>187.3609567124905</v>
+        <v>185.120241852071</v>
       </c>
       <c r="E62">
-        <v>319.8799999999999</v>
+        <v>326.478</v>
       </c>
       <c r="F62">
-        <v>395.8799999999999</v>
+        <v>402.478</v>
       </c>
       <c r="G62">
         <v>66.09999999999999</v>
@@ -6359,37 +6359,37 @@
         <v>35.635</v>
       </c>
       <c r="M62">
-        <v>93.34850399999999</v>
+        <v>94.90431239999999</v>
       </c>
       <c r="N62">
-        <v>-57.71350399999999</v>
+        <v>-59.2693124</v>
       </c>
       <c r="O62">
-        <v>-5.771350399999999</v>
+        <v>-5.92693124</v>
       </c>
       <c r="P62">
-        <v>-51.9421536</v>
+        <v>-53.34238116</v>
       </c>
       <c r="Q62">
-        <v>-50.4521536</v>
+        <v>-51.85238115999999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1667310444870983</v>
+        <v>0.169831840499588</v>
       </c>
       <c r="T62">
-        <v>2.423900736390981</v>
+        <v>2.486052037324084</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.0381741522070884</v>
+        <v>0.03754834643320171</v>
       </c>
       <c r="W62">
-        <v>0.2267985349095686</v>
+        <v>0.2269460999110511</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.381741522070884</v>
+        <v>0.375483464332017</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2046715387405805</v>
+        <v>0.2065715387405804</v>
       </c>
       <c r="C63">
-        <v>-151.2577581479289</v>
+        <v>-160.0435114174083</v>
       </c>
       <c r="D63">
-        <v>185.120241852071</v>
+        <v>182.9324885825917</v>
       </c>
       <c r="E63">
-        <v>326.478</v>
+        <v>333.076</v>
       </c>
       <c r="F63">
-        <v>402.478</v>
+        <v>409.076</v>
       </c>
       <c r="G63">
         <v>66.09999999999999</v>
@@ -6441,37 +6441,37 @@
         <v>35.635</v>
       </c>
       <c r="M63">
-        <v>94.90431239999999</v>
+        <v>96.4601208</v>
       </c>
       <c r="N63">
-        <v>-59.2693124</v>
+        <v>-60.8251208</v>
       </c>
       <c r="O63">
-        <v>-5.92693124</v>
+        <v>-6.082512080000001</v>
       </c>
       <c r="P63">
-        <v>-53.34238116</v>
+        <v>-54.74260872</v>
       </c>
       <c r="Q63">
-        <v>-51.85238115999999</v>
+        <v>-53.25260872</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.169831840499588</v>
+        <v>0.1730958363022087</v>
       </c>
       <c r="T63">
-        <v>2.486052037324084</v>
+        <v>2.551474459358928</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.03754834643320171</v>
+        <v>0.03694272794234361</v>
       </c>
       <c r="W63">
-        <v>0.2269460999110511</v>
+        <v>0.2270889047511954</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.375483464332017</v>
+        <v>0.3694272794234361</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2065715387405804</v>
+        <v>0.2084715387405805</v>
       </c>
       <c r="C64">
-        <v>-160.0435114174083</v>
+        <v>-168.7781588666048</v>
       </c>
       <c r="D64">
-        <v>182.9324885825917</v>
+        <v>180.7958411333952</v>
       </c>
       <c r="E64">
-        <v>333.076</v>
+        <v>339.674</v>
       </c>
       <c r="F64">
-        <v>409.076</v>
+        <v>415.674</v>
       </c>
       <c r="G64">
         <v>66.09999999999999</v>
@@ -6523,37 +6523,37 @@
         <v>35.635</v>
       </c>
       <c r="M64">
-        <v>96.4601208</v>
+        <v>98.0159292</v>
       </c>
       <c r="N64">
-        <v>-60.8251208</v>
+        <v>-62.3809292</v>
       </c>
       <c r="O64">
-        <v>-6.082512080000001</v>
+        <v>-6.238092920000001</v>
       </c>
       <c r="P64">
-        <v>-54.74260872</v>
+        <v>-56.14283628</v>
       </c>
       <c r="Q64">
-        <v>-53.25260872</v>
+        <v>-54.65283628</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1730958363022087</v>
+        <v>0.1765362643103766</v>
       </c>
       <c r="T64">
-        <v>2.551474459358928</v>
+        <v>2.620433228530791</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.03694272794234361</v>
+        <v>0.03635633543532228</v>
       </c>
       <c r="W64">
-        <v>0.2270889047511954</v>
+        <v>0.227227176104351</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3694272794234361</v>
+        <v>0.3635633543532228</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2084715387405805</v>
+        <v>0.2103715387405805</v>
       </c>
       <c r="C65">
-        <v>-168.7781588666048</v>
+        <v>-177.463470565713</v>
       </c>
       <c r="D65">
-        <v>180.7958411333952</v>
+        <v>178.708529434287</v>
       </c>
       <c r="E65">
-        <v>339.674</v>
+        <v>346.272</v>
       </c>
       <c r="F65">
-        <v>415.674</v>
+        <v>422.272</v>
       </c>
       <c r="G65">
         <v>66.09999999999999</v>
@@ -6605,37 +6605,37 @@
         <v>35.635</v>
       </c>
       <c r="M65">
-        <v>98.0159292</v>
+        <v>99.57173760000001</v>
       </c>
       <c r="N65">
-        <v>-62.3809292</v>
+        <v>-63.93673760000001</v>
       </c>
       <c r="O65">
-        <v>-6.238092920000001</v>
+        <v>-6.393673760000001</v>
       </c>
       <c r="P65">
-        <v>-56.14283628</v>
+        <v>-57.54306384000001</v>
       </c>
       <c r="Q65">
-        <v>-54.65283628</v>
+        <v>-56.05306384000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1765362643103766</v>
+        <v>0.180167827207887</v>
       </c>
       <c r="T65">
-        <v>2.620433228530791</v>
+        <v>2.693223040434424</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.03635633543532228</v>
+        <v>0.03578826769414536</v>
       </c>
       <c r="W65">
-        <v>0.227227176104351</v>
+        <v>0.2273611264777205</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3635633543532228</v>
+        <v>0.3578826769414537</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2103715387405805</v>
+        <v>0.2122715387405805</v>
       </c>
       <c r="C66">
-        <v>-177.463470565713</v>
+        <v>-186.1011357751172</v>
       </c>
       <c r="D66">
-        <v>178.708529434287</v>
+        <v>176.6688642248828</v>
       </c>
       <c r="E66">
-        <v>346.272</v>
+        <v>352.87</v>
       </c>
       <c r="F66">
-        <v>422.272</v>
+        <v>428.87</v>
       </c>
       <c r="G66">
         <v>66.09999999999999</v>
@@ -6687,37 +6687,37 @@
         <v>35.635</v>
       </c>
       <c r="M66">
-        <v>99.57173760000001</v>
+        <v>101.127546</v>
       </c>
       <c r="N66">
-        <v>-63.93673760000001</v>
+        <v>-65.492546</v>
       </c>
       <c r="O66">
-        <v>-6.393673760000001</v>
+        <v>-6.549254600000001</v>
       </c>
       <c r="P66">
-        <v>-57.54306384000001</v>
+        <v>-58.94329140000001</v>
       </c>
       <c r="Q66">
-        <v>-56.05306384000001</v>
+        <v>-57.4532914</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.180167827207887</v>
+        <v>0.1840069079852552</v>
       </c>
       <c r="T66">
-        <v>2.693223040434424</v>
+        <v>2.770172270161122</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.03578826769414536</v>
+        <v>0.03523767896038928</v>
       </c>
       <c r="W66">
-        <v>0.2273611264777205</v>
+        <v>0.2274909553011402</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3578826769414537</v>
+        <v>0.352376789603893</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2122715387405805</v>
+        <v>0.2141715387405805</v>
       </c>
       <c r="C67">
-        <v>-186.1011357751172</v>
+        <v>-194.6927675049101</v>
       </c>
       <c r="D67">
-        <v>176.6688642248828</v>
+        <v>174.6752324950899</v>
       </c>
       <c r="E67">
-        <v>352.87</v>
+        <v>359.468</v>
       </c>
       <c r="F67">
-        <v>428.87</v>
+        <v>435.468</v>
       </c>
       <c r="G67">
         <v>66.09999999999999</v>
@@ -6769,37 +6769,37 @@
         <v>35.635</v>
       </c>
       <c r="M67">
-        <v>101.127546</v>
+        <v>102.6833544</v>
       </c>
       <c r="N67">
-        <v>-65.492546</v>
+        <v>-67.04835440000002</v>
       </c>
       <c r="O67">
-        <v>-6.549254600000001</v>
+        <v>-6.704835440000003</v>
       </c>
       <c r="P67">
-        <v>-58.94329140000001</v>
+        <v>-60.34351896000002</v>
       </c>
       <c r="Q67">
-        <v>-57.4532914</v>
+        <v>-58.85351896000002</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1840069079852552</v>
+        <v>0.1880718170436451</v>
       </c>
       <c r="T67">
-        <v>2.770172270161122</v>
+        <v>2.851647925165861</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.03523767896038928</v>
+        <v>0.03470377473371672</v>
       </c>
       <c r="W67">
-        <v>0.2274909553011402</v>
+        <v>0.2276168499177896</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.352376789603893</v>
+        <v>0.3470377473371671</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2141715387405805</v>
+        <v>0.2160715387405805</v>
       </c>
       <c r="C68">
-        <v>-194.6927675049101</v>
+        <v>-203.2399067691433</v>
       </c>
       <c r="D68">
-        <v>174.6752324950899</v>
+        <v>172.7260932308566</v>
       </c>
       <c r="E68">
-        <v>359.468</v>
+        <v>366.066</v>
       </c>
       <c r="F68">
-        <v>435.468</v>
+        <v>442.066</v>
       </c>
       <c r="G68">
         <v>66.09999999999999</v>
@@ -6851,37 +6851,37 @@
         <v>35.635</v>
       </c>
       <c r="M68">
-        <v>102.6833544</v>
+        <v>104.2391628</v>
       </c>
       <c r="N68">
-        <v>-67.04835440000002</v>
+        <v>-68.60416280000001</v>
       </c>
       <c r="O68">
-        <v>-6.704835440000003</v>
+        <v>-6.860416280000002</v>
       </c>
       <c r="P68">
-        <v>-60.34351896000002</v>
+        <v>-61.74374652000001</v>
       </c>
       <c r="Q68">
-        <v>-58.85351896000002</v>
+        <v>-60.25374652000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1880718170436451</v>
+        <v>0.1923830842267859</v>
       </c>
       <c r="T68">
-        <v>2.851647925165861</v>
+        <v>2.938061498655736</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.03470377473371672</v>
+        <v>0.03418580794664632</v>
       </c>
       <c r="W68">
-        <v>0.2276168499177896</v>
+        <v>0.2277389864861808</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3470377473371671</v>
+        <v>0.3418580794664632</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2160715387405805</v>
+        <v>0.2179715387405805</v>
       </c>
       <c r="C69">
-        <v>-203.2399067691433</v>
+        <v>-211.7440265583908</v>
       </c>
       <c r="D69">
-        <v>172.7260932308566</v>
+        <v>170.8199734416092</v>
       </c>
       <c r="E69">
-        <v>366.066</v>
+        <v>372.664</v>
       </c>
       <c r="F69">
-        <v>442.066</v>
+        <v>448.664</v>
       </c>
       <c r="G69">
         <v>66.09999999999999</v>
@@ -6933,37 +6933,37 @@
         <v>35.635</v>
       </c>
       <c r="M69">
-        <v>104.2391628</v>
+        <v>105.7949712</v>
       </c>
       <c r="N69">
-        <v>-68.60416280000001</v>
+        <v>-70.1599712</v>
       </c>
       <c r="O69">
-        <v>-6.860416280000002</v>
+        <v>-7.015997120000001</v>
       </c>
       <c r="P69">
-        <v>-61.74374652000001</v>
+        <v>-63.14397408</v>
       </c>
       <c r="Q69">
-        <v>-60.25374652000001</v>
+        <v>-61.65397408</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1923830842267859</v>
+        <v>0.1969638056088729</v>
       </c>
       <c r="T69">
-        <v>2.938061498655736</v>
+        <v>3.029875920488728</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.03418580794664632</v>
+        <v>0.0336830754768427</v>
       </c>
       <c r="W69">
-        <v>0.2277389864861808</v>
+        <v>0.2278575308025605</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3418580794664632</v>
+        <v>0.3368307547684271</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2179715387405805</v>
+        <v>0.2198715387405805</v>
       </c>
       <c r="C70">
-        <v>-211.7440265583908</v>
+        <v>-220.2065355521486</v>
       </c>
       <c r="D70">
-        <v>170.8199734416092</v>
+        <v>168.9554644478514</v>
       </c>
       <c r="E70">
-        <v>372.664</v>
+        <v>379.262</v>
       </c>
       <c r="F70">
-        <v>448.664</v>
+        <v>455.262</v>
       </c>
       <c r="G70">
         <v>66.09999999999999</v>
@@ -7015,37 +7015,37 @@
         <v>35.635</v>
       </c>
       <c r="M70">
-        <v>105.7949712</v>
+        <v>107.3507796</v>
       </c>
       <c r="N70">
-        <v>-70.1599712</v>
+        <v>-71.71577960000002</v>
       </c>
       <c r="O70">
-        <v>-7.015997120000001</v>
+        <v>-7.171577960000002</v>
       </c>
       <c r="P70">
-        <v>-63.14397408</v>
+        <v>-64.54420164000001</v>
       </c>
       <c r="Q70">
-        <v>-61.65397408</v>
+        <v>-63.05420164000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1969638056088729</v>
+        <v>0.2018400574027076</v>
       </c>
       <c r="T70">
-        <v>3.029875920488728</v>
+        <v>3.127613853407719</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.0336830754768427</v>
+        <v>0.03319491496268556</v>
       </c>
       <c r="W70">
-        <v>0.2278575308025605</v>
+        <v>0.2279726390517988</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3368307547684271</v>
+        <v>0.3319491496268555</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2198715387405805</v>
+        <v>0.2217715387405805</v>
       </c>
       <c r="C71">
-        <v>-220.2065355521486</v>
+        <v>-228.628781590732</v>
       </c>
       <c r="D71">
-        <v>168.9554644478514</v>
+        <v>167.131218409268</v>
       </c>
       <c r="E71">
-        <v>379.262</v>
+        <v>385.86</v>
       </c>
       <c r="F71">
-        <v>455.262</v>
+        <v>461.86</v>
       </c>
       <c r="G71">
         <v>66.09999999999999</v>
@@ -7097,37 +7097,37 @@
         <v>35.635</v>
       </c>
       <c r="M71">
-        <v>107.3507796</v>
+        <v>108.906588</v>
       </c>
       <c r="N71">
-        <v>-71.71577960000002</v>
+        <v>-73.27158800000001</v>
       </c>
       <c r="O71">
-        <v>-7.171577960000002</v>
+        <v>-7.327158800000001</v>
       </c>
       <c r="P71">
-        <v>-64.54420164000001</v>
+        <v>-65.9444292</v>
       </c>
       <c r="Q71">
-        <v>-63.05420164000001</v>
+        <v>-64.45442920000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2018400574027076</v>
+        <v>0.2070413926494644</v>
       </c>
       <c r="T71">
-        <v>3.127613853407719</v>
+        <v>3.231867648521309</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.03319491496268556</v>
+        <v>0.03272070189179005</v>
       </c>
       <c r="W71">
-        <v>0.2279726390517988</v>
+        <v>0.2280844584939159</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3319491496268555</v>
+        <v>0.3272070189179005</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2217715387405805</v>
+        <v>0.2236715387405805</v>
       </c>
       <c r="C72">
-        <v>-228.628781590732</v>
+        <v>-237.0120549246562</v>
       </c>
       <c r="D72">
-        <v>167.131218409268</v>
+        <v>165.3459450753438</v>
       </c>
       <c r="E72">
-        <v>385.86</v>
+        <v>392.458</v>
       </c>
       <c r="F72">
-        <v>461.86</v>
+        <v>468.458</v>
       </c>
       <c r="G72">
         <v>66.09999999999999</v>
@@ -7179,37 +7179,37 @@
         <v>35.635</v>
       </c>
       <c r="M72">
-        <v>108.906588</v>
+        <v>110.4623964</v>
       </c>
       <c r="N72">
-        <v>-73.27158800000001</v>
+        <v>-74.82739640000003</v>
       </c>
       <c r="O72">
-        <v>-7.327158800000001</v>
+        <v>-7.482739640000003</v>
       </c>
       <c r="P72">
-        <v>-65.9444292</v>
+        <v>-67.34465676000002</v>
       </c>
       <c r="Q72">
-        <v>-64.45442920000001</v>
+        <v>-65.85465676000003</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2070413926494644</v>
+        <v>0.2126014406718598</v>
       </c>
       <c r="T72">
-        <v>3.231867648521309</v>
+        <v>3.343311360539286</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.03272070189179005</v>
+        <v>0.03225984693556765</v>
       </c>
       <c r="W72">
-        <v>0.2280844584939159</v>
+        <v>0.2281931280925932</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3272070189179005</v>
+        <v>0.3225984693556765</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2236715387405805</v>
+        <v>0.2255715387405804</v>
       </c>
       <c r="C73">
-        <v>-237.012054924656</v>
+        <v>-245.3575912579602</v>
       </c>
       <c r="D73">
-        <v>165.345945075344</v>
+        <v>163.5984087420398</v>
       </c>
       <c r="E73">
-        <v>392.458</v>
+        <v>399.0559999999999</v>
       </c>
       <c r="F73">
-        <v>468.458</v>
+        <v>475.0559999999999</v>
       </c>
       <c r="G73">
         <v>66.09999999999999</v>
@@ -7261,37 +7261,37 @@
         <v>35.635</v>
       </c>
       <c r="M73">
-        <v>110.4623964</v>
+        <v>112.0182048</v>
       </c>
       <c r="N73">
-        <v>-74.8273964</v>
+        <v>-76.38320479999999</v>
       </c>
       <c r="O73">
-        <v>-7.48273964</v>
+        <v>-7.638320479999999</v>
       </c>
       <c r="P73">
-        <v>-67.34465675999999</v>
+        <v>-68.74488431999998</v>
       </c>
       <c r="Q73">
-        <v>-65.85465676</v>
+        <v>-67.25488431999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2126014406718597</v>
+        <v>0.218558634981569</v>
       </c>
       <c r="T73">
-        <v>3.343311360539285</v>
+        <v>3.462715337701402</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.03225984693556765</v>
+        <v>0.031811793505907</v>
       </c>
       <c r="W73">
-        <v>0.2281931280925932</v>
+        <v>0.2282987790913071</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3225984693556766</v>
+        <v>0.31811793505907</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2255715387405804</v>
+        <v>0.2274715387405805</v>
       </c>
       <c r="C74">
-        <v>-245.3575912579602</v>
+        <v>-253.6665746005614</v>
       </c>
       <c r="D74">
-        <v>163.5984087420398</v>
+        <v>161.8874253994385</v>
       </c>
       <c r="E74">
-        <v>399.0559999999999</v>
+        <v>405.6539999999999</v>
       </c>
       <c r="F74">
-        <v>475.0559999999999</v>
+        <v>481.6539999999999</v>
       </c>
       <c r="G74">
         <v>66.09999999999999</v>
@@ -7343,37 +7343,37 @@
         <v>35.635</v>
       </c>
       <c r="M74">
-        <v>112.0182048</v>
+        <v>113.5740132</v>
       </c>
       <c r="N74">
-        <v>-76.38320479999999</v>
+        <v>-77.93901320000001</v>
       </c>
       <c r="O74">
-        <v>-7.638320479999999</v>
+        <v>-7.793901320000001</v>
       </c>
       <c r="P74">
-        <v>-68.74488431999998</v>
+        <v>-70.14511188</v>
       </c>
       <c r="Q74">
-        <v>-67.25488431999999</v>
+        <v>-68.65511188000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.218558634981569</v>
+        <v>0.2249571029438493</v>
       </c>
       <c r="T74">
-        <v>3.462715337701402</v>
+        <v>3.590964053912565</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.031811793505907</v>
+        <v>0.0313760155126754</v>
       </c>
       <c r="W74">
-        <v>0.2282987790913071</v>
+        <v>0.2284015355421112</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.31811793505907</v>
+        <v>0.3137601551267539</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2274715387405805</v>
+        <v>0.2293715387405804</v>
       </c>
       <c r="C75">
-        <v>-253.6665746005614</v>
+        <v>-261.9401399434744</v>
       </c>
       <c r="D75">
-        <v>161.8874253994385</v>
+        <v>160.2118600565256</v>
       </c>
       <c r="E75">
-        <v>405.6539999999999</v>
+        <v>412.252</v>
       </c>
       <c r="F75">
-        <v>481.6539999999999</v>
+        <v>488.252</v>
       </c>
       <c r="G75">
         <v>66.09999999999999</v>
@@ -7425,37 +7425,37 @@
         <v>35.635</v>
       </c>
       <c r="M75">
-        <v>113.5740132</v>
+        <v>115.1298216</v>
       </c>
       <c r="N75">
-        <v>-77.93901320000001</v>
+        <v>-79.49482159999999</v>
       </c>
       <c r="O75">
-        <v>-7.793901320000001</v>
+        <v>-7.94948216</v>
       </c>
       <c r="P75">
-        <v>-70.14511188</v>
+        <v>-71.54533943999999</v>
       </c>
       <c r="Q75">
-        <v>-68.65511188000001</v>
+        <v>-70.05533944</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2249571029438493</v>
+        <v>0.231847760749382</v>
       </c>
       <c r="T75">
-        <v>3.590964053912565</v>
+        <v>3.729078055986125</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.0313760155126754</v>
+        <v>0.03095201530304464</v>
       </c>
       <c r="W75">
-        <v>0.2284015355421112</v>
+        <v>0.2285015147915421</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3137601551267539</v>
+        <v>0.3095201530304466</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2293715387405804</v>
+        <v>0.2312715387405805</v>
       </c>
       <c r="C76">
-        <v>-261.9401399434744</v>
+        <v>-270.1793757695984</v>
       </c>
       <c r="D76">
-        <v>160.2118600565256</v>
+        <v>158.5706242304015</v>
       </c>
       <c r="E76">
-        <v>412.252</v>
+        <v>418.85</v>
       </c>
       <c r="F76">
-        <v>488.252</v>
+        <v>494.85</v>
       </c>
       <c r="G76">
         <v>66.09999999999999</v>
@@ -7507,37 +7507,37 @@
         <v>35.635</v>
       </c>
       <c r="M76">
-        <v>115.1298216</v>
+        <v>116.68563</v>
       </c>
       <c r="N76">
-        <v>-79.49482159999999</v>
+        <v>-81.05063000000001</v>
       </c>
       <c r="O76">
-        <v>-7.94948216</v>
+        <v>-8.105063000000001</v>
       </c>
       <c r="P76">
-        <v>-71.54533943999999</v>
+        <v>-72.94556700000001</v>
       </c>
       <c r="Q76">
-        <v>-70.05533944</v>
+        <v>-71.45556700000002</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.231847760749382</v>
+        <v>0.2392896711793573</v>
       </c>
       <c r="T76">
-        <v>3.729078055986125</v>
+        <v>3.87824117822557</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.03095201530304464</v>
+        <v>0.03053932176567072</v>
       </c>
       <c r="W76">
-        <v>0.2285015147915421</v>
+        <v>0.2285988279276548</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3095201530304466</v>
+        <v>0.3053932176567071</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2312715387405805</v>
+        <v>0.2331715387405805</v>
       </c>
       <c r="C77">
-        <v>-270.1793757695984</v>
+        <v>-278.3853264117444</v>
       </c>
       <c r="D77">
-        <v>158.5706242304015</v>
+        <v>156.9626735882556</v>
       </c>
       <c r="E77">
-        <v>418.85</v>
+        <v>425.448</v>
       </c>
       <c r="F77">
-        <v>494.85</v>
+        <v>501.448</v>
       </c>
       <c r="G77">
         <v>66.09999999999999</v>
@@ -7589,37 +7589,37 @@
         <v>35.635</v>
       </c>
       <c r="M77">
-        <v>116.68563</v>
+        <v>118.2414384</v>
       </c>
       <c r="N77">
-        <v>-81.05063000000001</v>
+        <v>-82.6064384</v>
       </c>
       <c r="O77">
-        <v>-8.105063000000001</v>
+        <v>-8.26064384</v>
       </c>
       <c r="P77">
-        <v>-72.94556700000001</v>
+        <v>-74.34579456</v>
       </c>
       <c r="Q77">
-        <v>-71.45556700000002</v>
+        <v>-72.85579456000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2392896711793573</v>
+        <v>0.2473517408118305</v>
       </c>
       <c r="T77">
-        <v>3.87824117822557</v>
+        <v>4.039834560651636</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.03053932176567072</v>
+        <v>0.03013748858454347</v>
       </c>
       <c r="W77">
-        <v>0.2285988279276548</v>
+        <v>0.2286935801917647</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3053932176567071</v>
+        <v>0.3013748858454347</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2331715387405805</v>
+        <v>0.2350715387405805</v>
       </c>
       <c r="C78">
-        <v>-278.3853264117444</v>
+        <v>-286.5589942686345</v>
       </c>
       <c r="D78">
-        <v>156.9626735882556</v>
+        <v>155.3870057313655</v>
       </c>
       <c r="E78">
-        <v>425.448</v>
+        <v>432.046</v>
       </c>
       <c r="F78">
-        <v>501.448</v>
+        <v>508.046</v>
       </c>
       <c r="G78">
         <v>66.09999999999999</v>
@@ -7671,37 +7671,37 @@
         <v>35.635</v>
       </c>
       <c r="M78">
-        <v>118.2414384</v>
+        <v>119.7972468</v>
       </c>
       <c r="N78">
-        <v>-82.6064384</v>
+        <v>-84.16224679999999</v>
       </c>
       <c r="O78">
-        <v>-8.26064384</v>
+        <v>-8.416224679999999</v>
       </c>
       <c r="P78">
-        <v>-74.34579456</v>
+        <v>-75.74602211999999</v>
       </c>
       <c r="Q78">
-        <v>-72.85579456000001</v>
+        <v>-74.25602212</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2473517408118305</v>
+        <v>0.2561148599775623</v>
       </c>
       <c r="T78">
-        <v>4.039834560651636</v>
+        <v>4.215479541549533</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.03013748858454347</v>
+        <v>0.02974609262890005</v>
       </c>
       <c r="W78">
-        <v>0.2286935801917647</v>
+        <v>0.2287858713581054</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3013748858454347</v>
+        <v>0.2974609262890006</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2350715387405805</v>
+        <v>0.2369715387405805</v>
       </c>
       <c r="C79">
-        <v>-286.5589942686345</v>
+        <v>-294.7013418887593</v>
       </c>
       <c r="D79">
-        <v>155.3870057313655</v>
+        <v>153.8426581112407</v>
       </c>
       <c r="E79">
-        <v>432.046</v>
+        <v>438.644</v>
       </c>
       <c r="F79">
-        <v>508.046</v>
+        <v>514.644</v>
       </c>
       <c r="G79">
         <v>66.09999999999999</v>
@@ -7753,37 +7753,37 @@
         <v>35.635</v>
       </c>
       <c r="M79">
-        <v>119.7972468</v>
+        <v>121.3530552</v>
       </c>
       <c r="N79">
-        <v>-84.16224679999999</v>
+        <v>-85.71805520000001</v>
       </c>
       <c r="O79">
-        <v>-8.416224679999999</v>
+        <v>-8.571805520000002</v>
       </c>
       <c r="P79">
-        <v>-75.74602211999999</v>
+        <v>-77.14624968000001</v>
       </c>
       <c r="Q79">
-        <v>-74.25602212</v>
+        <v>-75.65624968000002</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2561148599775623</v>
+        <v>0.2656746263401787</v>
       </c>
       <c r="T79">
-        <v>4.215479541549533</v>
+        <v>4.407092247983604</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.02974609262890005</v>
+        <v>0.02936473246699108</v>
       </c>
       <c r="W79">
-        <v>0.2287858713581054</v>
+        <v>0.2288757960842835</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2974609262890006</v>
+        <v>0.2936473246699106</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2369715387405805</v>
+        <v>0.2388715387405805</v>
       </c>
       <c r="C80">
-        <v>-294.7013418887593</v>
+        <v>-302.8132939311891</v>
       </c>
       <c r="D80">
-        <v>153.8426581112407</v>
+        <v>152.3287060688109</v>
       </c>
       <c r="E80">
-        <v>438.644</v>
+        <v>445.242</v>
       </c>
       <c r="F80">
-        <v>514.644</v>
+        <v>521.242</v>
       </c>
       <c r="G80">
         <v>66.09999999999999</v>
@@ -7835,37 +7835,37 @@
         <v>35.635</v>
       </c>
       <c r="M80">
-        <v>121.3530552</v>
+        <v>122.9088636</v>
       </c>
       <c r="N80">
-        <v>-85.71805520000001</v>
+        <v>-87.2738636</v>
       </c>
       <c r="O80">
-        <v>-8.571805520000002</v>
+        <v>-8.727386360000001</v>
       </c>
       <c r="P80">
-        <v>-77.14624968000001</v>
+        <v>-78.54647724</v>
       </c>
       <c r="Q80">
-        <v>-75.65624968000002</v>
+        <v>-77.05647724000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2656746263401787</v>
+        <v>0.276144846642092</v>
       </c>
       <c r="T80">
-        <v>4.407092247983604</v>
+        <v>4.61695378360187</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.02936473246699108</v>
+        <v>0.02899302699272537</v>
       </c>
       <c r="W80">
-        <v>0.2288757960842835</v>
+        <v>0.2289634442351154</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2936473246699106</v>
+        <v>0.2899302699272536</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2388715387405805</v>
+        <v>0.2407715387405804</v>
       </c>
       <c r="C81">
-        <v>-302.8132939311891</v>
+        <v>-310.8957390117392</v>
       </c>
       <c r="D81">
-        <v>152.3287060688109</v>
+        <v>150.8442609882608</v>
       </c>
       <c r="E81">
-        <v>445.242</v>
+        <v>451.84</v>
       </c>
       <c r="F81">
-        <v>521.242</v>
+        <v>527.84</v>
       </c>
       <c r="G81">
         <v>66.09999999999999</v>
@@ -7917,37 +7917,37 @@
         <v>35.635</v>
       </c>
       <c r="M81">
-        <v>122.9088636</v>
+        <v>124.464672</v>
       </c>
       <c r="N81">
-        <v>-87.2738636</v>
+        <v>-88.82967200000002</v>
       </c>
       <c r="O81">
-        <v>-8.727386360000001</v>
+        <v>-8.882967200000001</v>
       </c>
       <c r="P81">
-        <v>-78.54647724</v>
+        <v>-79.94670480000002</v>
       </c>
       <c r="Q81">
-        <v>-77.05647724000001</v>
+        <v>-78.45670480000003</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.276144846642092</v>
+        <v>0.2876620889741967</v>
       </c>
       <c r="T81">
-        <v>4.61695378360187</v>
+        <v>4.847801472781964</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.02899302699272537</v>
+        <v>0.02863061415531629</v>
       </c>
       <c r="W81">
-        <v>0.2289634442351154</v>
+        <v>0.2290489011821764</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2899302699272536</v>
+        <v>0.2863061415531629</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2407715387405804</v>
+        <v>0.2426715387405805</v>
       </c>
       <c r="C82">
-        <v>-310.8957390117392</v>
+        <v>-318.9495314422303</v>
       </c>
       <c r="D82">
-        <v>150.8442609882608</v>
+        <v>149.3884685577697</v>
       </c>
       <c r="E82">
-        <v>451.84</v>
+        <v>458.438</v>
       </c>
       <c r="F82">
-        <v>527.84</v>
+        <v>534.438</v>
       </c>
       <c r="G82">
         <v>66.09999999999999</v>
@@ -7999,37 +7999,37 @@
         <v>35.635</v>
       </c>
       <c r="M82">
-        <v>124.464672</v>
+        <v>126.0204804</v>
       </c>
       <c r="N82">
-        <v>-88.82967200000002</v>
+        <v>-90.38548040000001</v>
       </c>
       <c r="O82">
-        <v>-8.882967200000001</v>
+        <v>-9.03854804</v>
       </c>
       <c r="P82">
-        <v>-79.94670480000002</v>
+        <v>-81.34693236000001</v>
       </c>
       <c r="Q82">
-        <v>-78.45670480000003</v>
+        <v>-79.85693236000002</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2876620889741967</v>
+        <v>0.3003916726044176</v>
       </c>
       <c r="T82">
-        <v>4.847801472781964</v>
+        <v>5.102948918717858</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.02863061415531629</v>
+        <v>0.02827714978302845</v>
       </c>
       <c r="W82">
-        <v>0.2290489011821764</v>
+        <v>0.2291322480811619</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2863061415531629</v>
+        <v>0.2827714978302843</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2426715387405805</v>
+        <v>0.2445715387405805</v>
       </c>
       <c r="C83">
-        <v>-318.9495314422303</v>
+        <v>-326.975492869999</v>
       </c>
       <c r="D83">
-        <v>149.3884685577697</v>
+        <v>147.960507130001</v>
       </c>
       <c r="E83">
-        <v>458.438</v>
+        <v>465.0360000000001</v>
       </c>
       <c r="F83">
-        <v>534.438</v>
+        <v>541.0360000000001</v>
       </c>
       <c r="G83">
         <v>66.09999999999999</v>
@@ -8081,37 +8081,37 @@
         <v>35.635</v>
       </c>
       <c r="M83">
-        <v>126.0204804</v>
+        <v>127.5762888</v>
       </c>
       <c r="N83">
-        <v>-90.38548040000001</v>
+        <v>-91.94128880000002</v>
       </c>
       <c r="O83">
-        <v>-9.03854804</v>
+        <v>-9.194128880000003</v>
       </c>
       <c r="P83">
-        <v>-81.34693236000001</v>
+        <v>-82.74715992000002</v>
       </c>
       <c r="Q83">
-        <v>-79.85693236000002</v>
+        <v>-81.25715992000002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3003916726044176</v>
+        <v>0.3145356544157741</v>
       </c>
       <c r="T83">
-        <v>5.102948918717858</v>
+        <v>5.38644608086885</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.02827714978302845</v>
+        <v>0.02793230649299151</v>
       </c>
       <c r="W83">
-        <v>0.2291322480811619</v>
+        <v>0.2292135621289526</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2827714978302843</v>
+        <v>0.279323064929915</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2445715387405805</v>
+        <v>0.2464715387405805</v>
       </c>
       <c r="C84">
-        <v>-326.975492869999</v>
+        <v>-334.9744138242676</v>
       </c>
       <c r="D84">
-        <v>147.960507130001</v>
+        <v>146.5595861757324</v>
       </c>
       <c r="E84">
-        <v>465.0360000000001</v>
+        <v>471.634</v>
       </c>
       <c r="F84">
-        <v>541.0360000000001</v>
+        <v>547.634</v>
       </c>
       <c r="G84">
         <v>66.09999999999999</v>
@@ -8163,37 +8163,37 @@
         <v>35.635</v>
       </c>
       <c r="M84">
-        <v>127.5762888</v>
+        <v>129.1320972</v>
       </c>
       <c r="N84">
-        <v>-91.94128880000002</v>
+        <v>-93.49709720000001</v>
       </c>
       <c r="O84">
-        <v>-9.194128880000003</v>
+        <v>-9.349709720000002</v>
       </c>
       <c r="P84">
-        <v>-82.74715992000002</v>
+        <v>-84.14738748000001</v>
       </c>
       <c r="Q84">
-        <v>-81.25715992000002</v>
+        <v>-82.65738748000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3145356544157741</v>
+        <v>0.3303436340872902</v>
       </c>
       <c r="T84">
-        <v>5.38644608086885</v>
+        <v>5.703295850331724</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.02793230649299151</v>
+        <v>0.02759577267982294</v>
       </c>
       <c r="W84">
-        <v>0.2292135621289526</v>
+        <v>0.2292929168020978</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.279323064929915</v>
+        <v>0.2759577267982293</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2464715387405805</v>
+        <v>0.2483715387405805</v>
       </c>
       <c r="C85">
-        <v>-334.9744138242676</v>
+        <v>-342.9470551754917</v>
       </c>
       <c r="D85">
-        <v>146.5595861757324</v>
+        <v>145.1849448245083</v>
       </c>
       <c r="E85">
-        <v>471.634</v>
+        <v>478.232</v>
       </c>
       <c r="F85">
-        <v>547.634</v>
+        <v>554.232</v>
       </c>
       <c r="G85">
         <v>66.09999999999999</v>
@@ -8245,37 +8245,37 @@
         <v>35.635</v>
       </c>
       <c r="M85">
-        <v>129.1320972</v>
+        <v>130.6879056</v>
       </c>
       <c r="N85">
-        <v>-93.49709720000001</v>
+        <v>-95.0529056</v>
       </c>
       <c r="O85">
-        <v>-9.349709720000002</v>
+        <v>-9.505290560000001</v>
       </c>
       <c r="P85">
-        <v>-84.14738748000001</v>
+        <v>-85.54761504</v>
       </c>
       <c r="Q85">
-        <v>-82.65738748000001</v>
+        <v>-84.05761504</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3303436340872902</v>
+        <v>0.3481276112177459</v>
       </c>
       <c r="T85">
-        <v>5.703295850331724</v>
+        <v>6.059751840977458</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.02759577267982294</v>
+        <v>0.02726725157649171</v>
       </c>
       <c r="W85">
-        <v>0.2292929168020978</v>
+        <v>0.2293703820782633</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2759577267982293</v>
+        <v>0.272672515764917</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2483715387405805</v>
+        <v>0.2502715387405804</v>
       </c>
       <c r="C86">
-        <v>-342.9470551754915</v>
+        <v>-350.8941495133424</v>
       </c>
       <c r="D86">
-        <v>145.1849448245084</v>
+        <v>143.8358504866575</v>
       </c>
       <c r="E86">
-        <v>478.232</v>
+        <v>484.8299999999999</v>
       </c>
       <c r="F86">
-        <v>554.232</v>
+        <v>560.8299999999999</v>
       </c>
       <c r="G86">
         <v>66.09999999999999</v>
@@ -8327,37 +8327,37 @@
         <v>35.635</v>
       </c>
       <c r="M86">
-        <v>130.6879056</v>
+        <v>132.243714</v>
       </c>
       <c r="N86">
-        <v>-95.0529056</v>
+        <v>-96.60871399999999</v>
       </c>
       <c r="O86">
-        <v>-9.505290560000001</v>
+        <v>-9.6608714</v>
       </c>
       <c r="P86">
-        <v>-85.54761504</v>
+        <v>-86.94784259999999</v>
       </c>
       <c r="Q86">
-        <v>-84.05761504</v>
+        <v>-85.45784259999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3481276112177458</v>
+        <v>0.3682827852989288</v>
       </c>
       <c r="T86">
-        <v>6.059751840977454</v>
+        <v>6.463735297042617</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.02726725157649171</v>
+        <v>0.02694646038147416</v>
       </c>
       <c r="W86">
-        <v>0.2293703820782633</v>
+        <v>0.2294460246420484</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.272672515764917</v>
+        <v>0.2694646038147416</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2502715387405804</v>
+        <v>0.2521715387405805</v>
       </c>
       <c r="C87">
-        <v>-350.8941495133424</v>
+        <v>-358.8164024485701</v>
       </c>
       <c r="D87">
-        <v>143.8358504866575</v>
+        <v>142.5115975514299</v>
       </c>
       <c r="E87">
-        <v>484.8299999999999</v>
+        <v>491.428</v>
       </c>
       <c r="F87">
-        <v>560.8299999999999</v>
+        <v>567.428</v>
       </c>
       <c r="G87">
         <v>66.09999999999999</v>
@@ -8409,37 +8409,37 @@
         <v>35.635</v>
       </c>
       <c r="M87">
-        <v>132.243714</v>
+        <v>133.7995224</v>
       </c>
       <c r="N87">
-        <v>-96.60871399999999</v>
+        <v>-98.16452240000001</v>
       </c>
       <c r="O87">
-        <v>-9.6608714</v>
+        <v>-9.816452240000002</v>
       </c>
       <c r="P87">
-        <v>-86.94784259999999</v>
+        <v>-88.34807016000001</v>
       </c>
       <c r="Q87">
-        <v>-85.45784259999999</v>
+        <v>-86.85807016000001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3682827852989288</v>
+        <v>0.391317269963138</v>
       </c>
       <c r="T87">
-        <v>6.463735297042617</v>
+        <v>6.925430675402805</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.02694646038147416</v>
+        <v>0.02663312944680586</v>
       </c>
       <c r="W87">
-        <v>0.2294460246420484</v>
+        <v>0.2295199080764432</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2694646038147416</v>
+        <v>0.2663312944680585</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2521715387405805</v>
+        <v>0.2540715387405805</v>
       </c>
       <c r="C88">
-        <v>-358.8164024485701</v>
+        <v>-366.714493843607</v>
       </c>
       <c r="D88">
-        <v>142.5115975514299</v>
+        <v>141.211506156393</v>
       </c>
       <c r="E88">
-        <v>491.428</v>
+        <v>498.026</v>
       </c>
       <c r="F88">
-        <v>567.428</v>
+        <v>574.026</v>
       </c>
       <c r="G88">
         <v>66.09999999999999</v>
@@ -8491,37 +8491,37 @@
         <v>35.635</v>
       </c>
       <c r="M88">
-        <v>133.7995224</v>
+        <v>135.3553308</v>
       </c>
       <c r="N88">
-        <v>-98.16452240000001</v>
+        <v>-99.7203308</v>
       </c>
       <c r="O88">
-        <v>-9.816452240000002</v>
+        <v>-9.972033080000001</v>
       </c>
       <c r="P88">
-        <v>-88.34807016000001</v>
+        <v>-89.74829772</v>
       </c>
       <c r="Q88">
-        <v>-86.85807016000001</v>
+        <v>-88.25829772</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.391317269963138</v>
+        <v>0.417895521498764</v>
       </c>
       <c r="T88">
-        <v>6.925430675402805</v>
+        <v>7.458156111972251</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.02663312944680586</v>
+        <v>0.02632700152212993</v>
       </c>
       <c r="W88">
-        <v>0.2295199080764432</v>
+        <v>0.2295920930410818</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2663312944680585</v>
+        <v>0.2632700152212992</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2540715387405805</v>
+        <v>0.2559715387405805</v>
       </c>
       <c r="C89">
-        <v>-366.714493843607</v>
+        <v>-374.5890789764223</v>
       </c>
       <c r="D89">
-        <v>141.211506156393</v>
+        <v>139.9349210235776</v>
       </c>
       <c r="E89">
-        <v>498.026</v>
+        <v>504.6239999999999</v>
       </c>
       <c r="F89">
-        <v>574.026</v>
+        <v>580.6239999999999</v>
       </c>
       <c r="G89">
         <v>66.09999999999999</v>
@@ -8573,37 +8573,37 @@
         <v>35.635</v>
       </c>
       <c r="M89">
-        <v>135.3553308</v>
+        <v>136.9111392</v>
       </c>
       <c r="N89">
-        <v>-99.7203308</v>
+        <v>-101.2761392</v>
       </c>
       <c r="O89">
-        <v>-9.972033080000001</v>
+        <v>-10.12761392</v>
       </c>
       <c r="P89">
-        <v>-89.74829772</v>
+        <v>-91.14852527999999</v>
       </c>
       <c r="Q89">
-        <v>-88.25829772</v>
+        <v>-89.65852527999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.417895521498764</v>
+        <v>0.448903481623661</v>
       </c>
       <c r="T89">
-        <v>7.458156111972251</v>
+        <v>8.079669121303272</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.02632700152212993</v>
+        <v>0.02602783105028755</v>
       </c>
       <c r="W89">
-        <v>0.2295920930410818</v>
+        <v>0.2296626374383422</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2632700152212992</v>
+        <v>0.2602783105028754</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2559715387405805</v>
+        <v>0.2578715387405804</v>
       </c>
       <c r="C90">
-        <v>-374.5890789764223</v>
+        <v>-382.4407896418126</v>
       </c>
       <c r="D90">
-        <v>139.9349210235776</v>
+        <v>138.6812103581874</v>
       </c>
       <c r="E90">
-        <v>504.6239999999999</v>
+        <v>511.222</v>
       </c>
       <c r="F90">
-        <v>580.6239999999999</v>
+        <v>587.222</v>
       </c>
       <c r="G90">
         <v>66.09999999999999</v>
@@ -8655,37 +8655,37 @@
         <v>35.635</v>
       </c>
       <c r="M90">
-        <v>136.9111392</v>
+        <v>138.4669476</v>
       </c>
       <c r="N90">
-        <v>-101.2761392</v>
+        <v>-102.8319476</v>
       </c>
       <c r="O90">
-        <v>-10.12761392</v>
+        <v>-10.28319476</v>
       </c>
       <c r="P90">
-        <v>-91.14852527999999</v>
+        <v>-92.54875284000001</v>
       </c>
       <c r="Q90">
-        <v>-89.65852527999999</v>
+        <v>-91.05875284000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.448903481623661</v>
+        <v>0.4855492526803575</v>
       </c>
       <c r="T90">
-        <v>8.079669121303272</v>
+        <v>8.814184495967208</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.02602783105028755</v>
+        <v>0.02573538351039667</v>
       </c>
       <c r="W90">
-        <v>0.2296626374383422</v>
+        <v>0.2297315965682485</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2602783105028754</v>
+        <v>0.2573538351039667</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2578715387405804</v>
+        <v>0.2597715387405805</v>
       </c>
       <c r="C91">
-        <v>-382.4407896418126</v>
+        <v>-390.2702351940176</v>
       </c>
       <c r="D91">
-        <v>138.6812103581874</v>
+        <v>137.4497648059823</v>
       </c>
       <c r="E91">
-        <v>511.222</v>
+        <v>517.8199999999999</v>
       </c>
       <c r="F91">
-        <v>587.222</v>
+        <v>593.8199999999999</v>
       </c>
       <c r="G91">
         <v>66.09999999999999</v>
@@ -8737,37 +8737,37 @@
         <v>35.635</v>
       </c>
       <c r="M91">
-        <v>138.4669476</v>
+        <v>140.022756</v>
       </c>
       <c r="N91">
-        <v>-102.8319476</v>
+        <v>-104.387756</v>
       </c>
       <c r="O91">
-        <v>-10.28319476</v>
+        <v>-10.4387756</v>
       </c>
       <c r="P91">
-        <v>-92.54875284000001</v>
+        <v>-93.9489804</v>
       </c>
       <c r="Q91">
-        <v>-91.05875284000001</v>
+        <v>-92.4589804</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4855492526803575</v>
+        <v>0.5295241779483932</v>
       </c>
       <c r="T91">
-        <v>8.814184495967208</v>
+        <v>9.695602945563929</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02573538351039667</v>
+        <v>0.0254494348047256</v>
       </c>
       <c r="W91">
-        <v>0.2297315965682485</v>
+        <v>0.2297990232730457</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2573538351039667</v>
+        <v>0.2544943480472559</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2597715387405805</v>
+        <v>0.2616715387405805</v>
       </c>
       <c r="C92">
-        <v>-390.2702351940176</v>
+        <v>-398.0780035342767</v>
       </c>
       <c r="D92">
-        <v>137.4497648059823</v>
+        <v>136.2399964657233</v>
       </c>
       <c r="E92">
-        <v>517.8199999999999</v>
+        <v>524.418</v>
       </c>
       <c r="F92">
-        <v>593.8199999999999</v>
+        <v>600.418</v>
       </c>
       <c r="G92">
         <v>66.09999999999999</v>
@@ -8819,37 +8819,37 @@
         <v>35.635</v>
       </c>
       <c r="M92">
-        <v>140.022756</v>
+        <v>141.5785644</v>
       </c>
       <c r="N92">
-        <v>-104.387756</v>
+        <v>-105.9435644</v>
       </c>
       <c r="O92">
-        <v>-10.4387756</v>
+        <v>-10.59435644</v>
       </c>
       <c r="P92">
-        <v>-93.9489804</v>
+        <v>-95.34920796000002</v>
       </c>
       <c r="Q92">
-        <v>-92.4589804</v>
+        <v>-93.85920796000002</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5295241779483932</v>
+        <v>0.5832713088315481</v>
       </c>
       <c r="T92">
-        <v>9.695602945563929</v>
+        <v>10.7728921617377</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.0254494348047256</v>
+        <v>0.02516977068599235</v>
       </c>
       <c r="W92">
-        <v>0.2297990232730457</v>
+        <v>0.229864968072243</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2544943480472559</v>
+        <v>0.2516977068599234</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2616715387405805</v>
+        <v>0.2635715387405805</v>
       </c>
       <c r="C93">
-        <v>-398.0780035342767</v>
+        <v>-405.864662046688</v>
       </c>
       <c r="D93">
-        <v>136.2399964657233</v>
+        <v>135.051337953312</v>
       </c>
       <c r="E93">
-        <v>524.418</v>
+        <v>531.016</v>
       </c>
       <c r="F93">
-        <v>600.418</v>
+        <v>607.016</v>
       </c>
       <c r="G93">
         <v>66.09999999999999</v>
@@ -8901,37 +8901,37 @@
         <v>35.635</v>
       </c>
       <c r="M93">
-        <v>141.5785644</v>
+        <v>143.1343728</v>
       </c>
       <c r="N93">
-        <v>-105.9435644</v>
+        <v>-107.4993728</v>
       </c>
       <c r="O93">
-        <v>-10.59435644</v>
+        <v>-10.74993728</v>
       </c>
       <c r="P93">
-        <v>-95.34920796000002</v>
+        <v>-96.74943552000001</v>
       </c>
       <c r="Q93">
-        <v>-93.85920796000002</v>
+        <v>-95.25943552000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5832713088315481</v>
+        <v>0.6504552224354918</v>
       </c>
       <c r="T93">
-        <v>10.7728921617377</v>
+        <v>12.11950368195492</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02516977068599235</v>
+        <v>0.02489618622201417</v>
       </c>
       <c r="W93">
-        <v>0.229864968072243</v>
+        <v>0.2299294792888491</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2516977068599234</v>
+        <v>0.2489618622201417</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2635715387405805</v>
+        <v>0.2654715387405805</v>
       </c>
       <c r="C94">
-        <v>-405.864662046688</v>
+        <v>-413.6307584855003</v>
       </c>
       <c r="D94">
-        <v>135.051337953312</v>
+        <v>133.8832415144997</v>
       </c>
       <c r="E94">
-        <v>531.016</v>
+        <v>537.614</v>
       </c>
       <c r="F94">
-        <v>607.016</v>
+        <v>613.614</v>
       </c>
       <c r="G94">
         <v>66.09999999999999</v>
@@ -8983,37 +8983,37 @@
         <v>35.635</v>
       </c>
       <c r="M94">
-        <v>143.1343728</v>
+        <v>144.6901812</v>
       </c>
       <c r="N94">
-        <v>-107.4993728</v>
+        <v>-109.0551812</v>
       </c>
       <c r="O94">
-        <v>-10.74993728</v>
+        <v>-10.90551812</v>
       </c>
       <c r="P94">
-        <v>-96.74943552000001</v>
+        <v>-98.14966308000001</v>
       </c>
       <c r="Q94">
-        <v>-95.25943552000001</v>
+        <v>-96.65966308000002</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6504552224354918</v>
+        <v>0.7368345399262765</v>
       </c>
       <c r="T94">
-        <v>12.11950368195492</v>
+        <v>13.85086135080562</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.02489618622201417</v>
+        <v>0.02462848529489574</v>
       </c>
       <c r="W94">
-        <v>0.2299294792888491</v>
+        <v>0.2299926031674636</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2489618622201417</v>
+        <v>0.2462848529489573</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2654715387405805</v>
+        <v>0.2673715387405804</v>
       </c>
       <c r="C95">
-        <v>-413.6307584855003</v>
+        <v>-421.376821816754</v>
       </c>
       <c r="D95">
-        <v>133.8832415144997</v>
+        <v>132.7351781832459</v>
       </c>
       <c r="E95">
-        <v>537.614</v>
+        <v>544.212</v>
       </c>
       <c r="F95">
-        <v>613.614</v>
+        <v>620.212</v>
       </c>
       <c r="G95">
         <v>66.09999999999999</v>
@@ -9065,37 +9065,37 @@
         <v>35.635</v>
       </c>
       <c r="M95">
-        <v>144.6901812</v>
+        <v>146.2459896</v>
       </c>
       <c r="N95">
-        <v>-109.0551812</v>
+        <v>-110.6109896</v>
       </c>
       <c r="O95">
-        <v>-10.90551812</v>
+        <v>-11.06109896</v>
       </c>
       <c r="P95">
-        <v>-98.14966308000001</v>
+        <v>-99.54989064</v>
       </c>
       <c r="Q95">
-        <v>-96.65966308000002</v>
+        <v>-98.05989064000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7368345399262765</v>
+        <v>0.8520069632473227</v>
       </c>
       <c r="T95">
-        <v>13.85086135080562</v>
+        <v>16.15933824260656</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.02462848529489574</v>
+        <v>0.02436648013218408</v>
       </c>
       <c r="W95">
-        <v>0.2299926031674636</v>
+        <v>0.230054383984831</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2462848529489573</v>
+        <v>0.2436648013218408</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2673715387405804</v>
+        <v>0.2692715387405805</v>
       </c>
       <c r="C96">
-        <v>-421.376821816754</v>
+        <v>-429.1033630169869</v>
       </c>
       <c r="D96">
-        <v>132.7351781832459</v>
+        <v>131.6066369830131</v>
       </c>
       <c r="E96">
-        <v>544.212</v>
+        <v>550.8099999999999</v>
       </c>
       <c r="F96">
-        <v>620.212</v>
+        <v>626.8099999999999</v>
       </c>
       <c r="G96">
         <v>66.09999999999999</v>
@@ -9147,37 +9147,37 @@
         <v>35.635</v>
       </c>
       <c r="M96">
-        <v>146.2459896</v>
+        <v>147.801798</v>
       </c>
       <c r="N96">
-        <v>-110.6109896</v>
+        <v>-112.166798</v>
       </c>
       <c r="O96">
-        <v>-11.06109896</v>
+        <v>-11.2166798</v>
       </c>
       <c r="P96">
-        <v>-99.54989064</v>
+        <v>-100.9501182</v>
       </c>
       <c r="Q96">
-        <v>-98.05989064000001</v>
+        <v>-99.4601182</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8520069632473227</v>
+        <v>1.013248355896788</v>
       </c>
       <c r="T96">
-        <v>16.15933824260656</v>
+        <v>19.39120589112788</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02436648013218408</v>
+        <v>0.02410999086763478</v>
       </c>
       <c r="W96">
-        <v>0.230054383984831</v>
+        <v>0.2301148641534117</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2436648013218408</v>
+        <v>0.2410999086763477</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2692715387405805</v>
+        <v>0.2711715387405805</v>
       </c>
       <c r="C97">
-        <v>-429.1033630169869</v>
+        <v>-436.8108758315378</v>
       </c>
       <c r="D97">
-        <v>131.6066369830131</v>
+        <v>130.4971241684622</v>
       </c>
       <c r="E97">
-        <v>550.8099999999999</v>
+        <v>557.408</v>
       </c>
       <c r="F97">
-        <v>626.8099999999999</v>
+        <v>633.408</v>
       </c>
       <c r="G97">
         <v>66.09999999999999</v>
@@ -9229,37 +9229,37 @@
         <v>35.635</v>
       </c>
       <c r="M97">
-        <v>147.801798</v>
+        <v>149.3576064</v>
       </c>
       <c r="N97">
-        <v>-112.166798</v>
+        <v>-113.7226064</v>
       </c>
       <c r="O97">
-        <v>-11.2166798</v>
+        <v>-11.37226064</v>
       </c>
       <c r="P97">
-        <v>-100.9501182</v>
+        <v>-102.35034576</v>
       </c>
       <c r="Q97">
-        <v>-99.4601182</v>
+        <v>-100.86034576</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.013248355896788</v>
+        <v>1.255110444870985</v>
       </c>
       <c r="T97">
-        <v>19.39120589112788</v>
+        <v>24.23900736390986</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.02410999086763478</v>
+        <v>0.02385884512943025</v>
       </c>
       <c r="W97">
-        <v>0.2301148641534117</v>
+        <v>0.2301740843184804</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2410999086763477</v>
+        <v>0.2385884512943024</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2711715387405805</v>
+        <v>0.2730715387405805</v>
       </c>
       <c r="C98">
-        <v>-436.8108758315377</v>
+        <v>-444.4998374948153</v>
       </c>
       <c r="D98">
-        <v>130.4971241684622</v>
+        <v>129.4061625051846</v>
       </c>
       <c r="E98">
-        <v>557.4079999999999</v>
+        <v>564.006</v>
       </c>
       <c r="F98">
-        <v>633.4079999999999</v>
+        <v>640.006</v>
       </c>
       <c r="G98">
         <v>66.09999999999999</v>
@@ -9311,37 +9311,37 @@
         <v>35.635</v>
       </c>
       <c r="M98">
-        <v>149.3576064</v>
+        <v>150.9134148</v>
       </c>
       <c r="N98">
-        <v>-113.7226064</v>
+        <v>-115.2784148</v>
       </c>
       <c r="O98">
-        <v>-11.37226064</v>
+        <v>-11.52784148</v>
       </c>
       <c r="P98">
-        <v>-102.35034576</v>
+        <v>-103.75057332</v>
       </c>
       <c r="Q98">
-        <v>-100.86034576</v>
+        <v>-102.26057332</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.255110444870982</v>
+        <v>1.658213926494643</v>
       </c>
       <c r="T98">
-        <v>24.2390073639098</v>
+        <v>32.31867648521306</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02385884512943025</v>
+        <v>0.02361287765386911</v>
       </c>
       <c r="W98">
-        <v>0.2301740843184804</v>
+        <v>0.2302320834492177</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2385884512943024</v>
+        <v>0.236128776538691</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2730715387405805</v>
+        <v>0.2749715387405804</v>
       </c>
       <c r="C99">
-        <v>-444.4998374948153</v>
+        <v>-452.1707094147363</v>
       </c>
       <c r="D99">
-        <v>129.4061625051846</v>
+        <v>128.3332905852637</v>
       </c>
       <c r="E99">
-        <v>564.006</v>
+        <v>570.6039999999999</v>
       </c>
       <c r="F99">
-        <v>640.006</v>
+        <v>646.6039999999999</v>
       </c>
       <c r="G99">
         <v>66.09999999999999</v>
@@ -9393,37 +9393,37 @@
         <v>35.635</v>
       </c>
       <c r="M99">
-        <v>150.9134148</v>
+        <v>152.4692232</v>
       </c>
       <c r="N99">
-        <v>-115.2784148</v>
+        <v>-116.8342232</v>
       </c>
       <c r="O99">
-        <v>-11.52784148</v>
+        <v>-11.68342232</v>
       </c>
       <c r="P99">
-        <v>-103.75057332</v>
+        <v>-105.15080088</v>
       </c>
       <c r="Q99">
-        <v>-102.26057332</v>
+        <v>-103.66080088</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.658213926494643</v>
+        <v>2.464420889741964</v>
       </c>
       <c r="T99">
-        <v>32.31867648521306</v>
+        <v>48.47801472781959</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02361287765386911</v>
+        <v>0.02337192992270718</v>
       </c>
       <c r="W99">
-        <v>0.2302320834492177</v>
+        <v>0.2302888989242257</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.236128776538691</v>
+        <v>0.2337192992270718</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2749715387405804</v>
+        <v>0.2768715387405805</v>
       </c>
       <c r="C100">
-        <v>-452.1707094147363</v>
+        <v>-459.823937823397</v>
       </c>
       <c r="D100">
-        <v>128.3332905852637</v>
+        <v>127.278062176603</v>
       </c>
       <c r="E100">
-        <v>570.6039999999999</v>
+        <v>577.202</v>
       </c>
       <c r="F100">
-        <v>646.6039999999999</v>
+        <v>653.202</v>
       </c>
       <c r="G100">
         <v>66.09999999999999</v>
@@ -9475,37 +9475,37 @@
         <v>35.635</v>
       </c>
       <c r="M100">
-        <v>152.4692232</v>
+        <v>154.0250316</v>
       </c>
       <c r="N100">
-        <v>-116.8342232</v>
+        <v>-118.3900316</v>
       </c>
       <c r="O100">
-        <v>-11.68342232</v>
+        <v>-11.83900316</v>
       </c>
       <c r="P100">
-        <v>-105.15080088</v>
+        <v>-106.55102844</v>
       </c>
       <c r="Q100">
-        <v>-103.66080088</v>
+        <v>-105.06102844</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.464420889741964</v>
+        <v>4.883041779483928</v>
       </c>
       <c r="T100">
-        <v>48.47801472781959</v>
+        <v>96.95602945563918</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02337192992270718</v>
+        <v>0.02313584982247782</v>
       </c>
       <c r="W100">
-        <v>0.2302888989242257</v>
+        <v>0.2303445666118597</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2337192992270718</v>
+        <v>0.2313584982247781</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2768715387405805</v>
-      </c>
-      <c r="C101">
-        <v>-459.823937823397</v>
-      </c>
-      <c r="D101">
-        <v>127.278062176603</v>
-      </c>
-      <c r="E101">
-        <v>577.202</v>
-      </c>
-      <c r="F101">
-        <v>653.202</v>
-      </c>
-      <c r="G101">
-        <v>66.09999999999999</v>
-      </c>
-      <c r="H101">
-        <v>583.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>37.125</v>
-      </c>
-      <c r="K101">
-        <v>1.49</v>
-      </c>
-      <c r="L101">
-        <v>35.635</v>
-      </c>
-      <c r="M101">
-        <v>154.0250316</v>
-      </c>
-      <c r="N101">
-        <v>-118.3900316</v>
-      </c>
-      <c r="O101">
-        <v>-11.83900316</v>
-      </c>
-      <c r="P101">
-        <v>-106.55102844</v>
-      </c>
-      <c r="Q101">
-        <v>-105.06102844</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.883041779483928</v>
-      </c>
-      <c r="T101">
-        <v>96.95602945563918</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02313584982247782</v>
-      </c>
-      <c r="W101">
-        <v>0.2303445666118597</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2313584982247781</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
